--- a/research/traditional_assets/database/data/qatar/qatar_retail_general.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_retail_general.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09372446890494121</v>
+        <v>0.09367124443603626</v>
       </c>
       <c r="C2">
-        <v>1014.403516394358</v>
+        <v>1005.377288329844</v>
       </c>
       <c r="D2">
-        <v>990.403516394358</v>
+        <v>991.5046722507117</v>
       </c>
       <c r="E2">
-        <v>-191.1383920867399</v>
+        <v>-181.0110081658725</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.1273839208674</v>
       </c>
       <c r="G2">
         <v>24</v>
@@ -1451,28 +1451,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5094074112196302</v>
       </c>
       <c r="N2">
-        <v>43.98999999999999</v>
+        <v>43.48059258878037</v>
       </c>
       <c r="O2">
-        <v>4.399</v>
+        <v>4.348059258878037</v>
       </c>
       <c r="P2">
-        <v>39.59099999999999</v>
+        <v>39.13253332990233</v>
       </c>
       <c r="Q2">
-        <v>68.39099999999999</v>
+        <v>67.93253332990233</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09372446890494121</v>
+        <v>0.09416014589498613</v>
       </c>
       <c r="T2">
-        <v>0.9605817593200963</v>
+        <v>0.9693143207684607</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>86.35524146513404</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09367124443603626</v>
+        <v>0.09361801996713132</v>
       </c>
       <c r="C3">
-        <v>1005.377288329844</v>
+        <v>996.3535115770194</v>
       </c>
       <c r="D3">
-        <v>991.5046722507117</v>
+        <v>992.6082794187541</v>
       </c>
       <c r="E3">
-        <v>-181.0110081658725</v>
+        <v>-170.8836242450051</v>
       </c>
       <c r="F3">
-        <v>10.1273839208674</v>
+        <v>20.2547678417348</v>
       </c>
       <c r="G3">
         <v>24</v>
@@ -1533,28 +1533,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M3">
-        <v>0.5094074112196302</v>
+        <v>1.01881482243926</v>
       </c>
       <c r="N3">
-        <v>43.48059258878037</v>
+        <v>42.97118517756073</v>
       </c>
       <c r="O3">
-        <v>4.348059258878037</v>
+        <v>4.297118517756074</v>
       </c>
       <c r="P3">
-        <v>39.13253332990233</v>
+        <v>38.67406665980466</v>
       </c>
       <c r="Q3">
-        <v>67.93253332990233</v>
+        <v>67.47406665980466</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09416014589498613</v>
+        <v>0.09460471425217482</v>
       </c>
       <c r="T3">
-        <v>0.9693143207684607</v>
+        <v>0.9782250977565878</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>86.35524146513404</v>
+        <v>43.17762073256702</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09361801996713132</v>
+        <v>0.09356479549822638</v>
       </c>
       <c r="C4">
-        <v>996.3535115770194</v>
+        <v>987.3321943303966</v>
       </c>
       <c r="D4">
-        <v>992.6082794187541</v>
+        <v>993.7143460929989</v>
       </c>
       <c r="E4">
-        <v>-170.8836242450051</v>
+        <v>-160.7562403241377</v>
       </c>
       <c r="F4">
-        <v>20.2547678417348</v>
+        <v>30.3821517626022</v>
       </c>
       <c r="G4">
         <v>24</v>
@@ -1615,28 +1615,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M4">
-        <v>1.01881482243926</v>
+        <v>1.52822223365889</v>
       </c>
       <c r="N4">
-        <v>42.97118517756073</v>
+        <v>42.46177776634111</v>
       </c>
       <c r="O4">
-        <v>4.297118517756074</v>
+        <v>4.246177776634111</v>
       </c>
       <c r="P4">
-        <v>38.67406665980466</v>
+        <v>38.21559998970699</v>
       </c>
       <c r="Q4">
-        <v>67.47406665980466</v>
+        <v>67.015599989707</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09460471425217482</v>
+        <v>0.09505844896724369</v>
       </c>
       <c r="T4">
-        <v>0.9782250977565878</v>
+        <v>0.9873196021052947</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>43.17762073256702</v>
+        <v>28.78508048837802</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09356479549822638</v>
+        <v>0.09351157102932145</v>
       </c>
       <c r="C5">
-        <v>987.3321943303966</v>
+        <v>978.3133448210561</v>
       </c>
       <c r="D5">
-        <v>993.7143460929989</v>
+        <v>994.8228805045258</v>
       </c>
       <c r="E5">
-        <v>-160.7562403241377</v>
+        <v>-150.6288564032703</v>
       </c>
       <c r="F5">
-        <v>30.3821517626022</v>
+        <v>40.5095356834696</v>
       </c>
       <c r="G5">
         <v>24</v>
@@ -1697,28 +1697,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M5">
-        <v>1.52822223365889</v>
+        <v>2.037629644878521</v>
       </c>
       <c r="N5">
-        <v>42.46177776634111</v>
+        <v>41.95237035512147</v>
       </c>
       <c r="O5">
-        <v>4.246177776634111</v>
+        <v>4.195237035512148</v>
       </c>
       <c r="P5">
-        <v>38.21559998970699</v>
+        <v>37.75713331960932</v>
       </c>
       <c r="Q5">
-        <v>67.015599989707</v>
+        <v>66.55713331960932</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09505844896724369</v>
+        <v>0.09552163648887652</v>
       </c>
       <c r="T5">
-        <v>0.9873196021052947</v>
+        <v>0.9966035752946</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.78508048837802</v>
+        <v>21.58881036628351</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09351157102932145</v>
+        <v>0.09345834656041649</v>
       </c>
       <c r="C6">
-        <v>978.3133448210561</v>
+        <v>969.2969713168476</v>
       </c>
       <c r="D6">
-        <v>994.8228805045258</v>
+        <v>995.9338909211846</v>
       </c>
       <c r="E6">
-        <v>-150.6288564032703</v>
+        <v>-140.5014724824029</v>
       </c>
       <c r="F6">
-        <v>40.5095356834696</v>
+        <v>50.636919604337</v>
       </c>
       <c r="G6">
         <v>24</v>
@@ -1779,28 +1779,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M6">
-        <v>2.037629644878521</v>
+        <v>2.547037056098151</v>
       </c>
       <c r="N6">
-        <v>41.95237035512147</v>
+        <v>41.44296294390185</v>
       </c>
       <c r="O6">
-        <v>4.195237035512148</v>
+        <v>4.144296294390185</v>
       </c>
       <c r="P6">
-        <v>37.75713331960932</v>
+        <v>37.29866664951166</v>
       </c>
       <c r="Q6">
-        <v>66.55713331960932</v>
+        <v>66.09866664951166</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09552163648887652</v>
+        <v>0.09599457532675421</v>
       </c>
       <c r="T6">
-        <v>0.9966035752946</v>
+        <v>1.006083000551048</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.58881036628351</v>
+        <v>17.27104829302681</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09345834656041649</v>
+        <v>0.09340512209151157</v>
       </c>
       <c r="C7">
-        <v>969.2969713168476</v>
+        <v>960.2830821225937</v>
       </c>
       <c r="D7">
-        <v>995.9338909211846</v>
+        <v>997.047385647798</v>
       </c>
       <c r="E7">
-        <v>-140.5014724824029</v>
+        <v>-130.3740885615355</v>
       </c>
       <c r="F7">
-        <v>50.636919604337</v>
+        <v>60.7643035252044</v>
       </c>
       <c r="G7">
         <v>24</v>
@@ -1861,28 +1861,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M7">
-        <v>2.547037056098151</v>
+        <v>3.056444467317781</v>
       </c>
       <c r="N7">
-        <v>41.44296294390185</v>
+        <v>40.93355553268221</v>
       </c>
       <c r="O7">
-        <v>4.144296294390185</v>
+        <v>4.093355553268221</v>
       </c>
       <c r="P7">
-        <v>37.29866664951166</v>
+        <v>36.840199979414</v>
       </c>
       <c r="Q7">
-        <v>66.09866664951166</v>
+        <v>65.64019997941399</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09599457532675421</v>
+        <v>0.09647757669309742</v>
       </c>
       <c r="T7">
-        <v>1.006083000551048</v>
+        <v>1.01576411570657</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.27104829302681</v>
+        <v>14.39254024418901</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09340512209151157</v>
+        <v>0.09344639762260662</v>
       </c>
       <c r="C8">
-        <v>960.2830821225937</v>
+        <v>949.2919674178063</v>
       </c>
       <c r="D8">
-        <v>997.047385647798</v>
+        <v>996.183654863878</v>
       </c>
       <c r="E8">
-        <v>-130.3740885615355</v>
+        <v>-120.2467046406681</v>
       </c>
       <c r="F8">
-        <v>60.7643035252044</v>
+        <v>70.89168744607178</v>
       </c>
       <c r="G8">
         <v>24</v>
@@ -1943,45 +1943,45 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M8">
-        <v>3.056444467317781</v>
+        <v>3.672189409706518</v>
       </c>
       <c r="N8">
-        <v>40.93355553268221</v>
+        <v>40.31781059029348</v>
       </c>
       <c r="O8">
-        <v>4.093355553268221</v>
+        <v>4.031781059029348</v>
       </c>
       <c r="P8">
-        <v>36.840199979414</v>
+        <v>36.28602953126413</v>
       </c>
       <c r="Q8">
-        <v>65.64019997941399</v>
+        <v>65.08602953126413</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09647757669309742</v>
+        <v>0.09697096518559851</v>
       </c>
       <c r="T8">
-        <v>1.01576411570657</v>
+        <v>1.025653426886941</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.1</v>
       </c>
       <c r="W8">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.39254024418901</v>
+        <v>11.97922957996757</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09344639762260661</v>
+        <v>0.09340667315370167</v>
       </c>
       <c r="C9">
-        <v>949.2919674178063</v>
+        <v>939.9958297067609</v>
       </c>
       <c r="D9">
-        <v>996.1836548638781</v>
+        <v>997.0149010737001</v>
       </c>
       <c r="E9">
-        <v>-120.2467046406681</v>
+        <v>-110.1193207198007</v>
       </c>
       <c r="F9">
-        <v>70.8916874460718</v>
+        <v>81.0190713669392</v>
       </c>
       <c r="G9">
         <v>24</v>
@@ -2025,28 +2025,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M9">
-        <v>3.672189409706519</v>
+        <v>4.19678789680745</v>
       </c>
       <c r="N9">
-        <v>40.31781059029348</v>
+        <v>39.79321210319254</v>
       </c>
       <c r="O9">
-        <v>4.031781059029348</v>
+        <v>3.979321210319255</v>
       </c>
       <c r="P9">
-        <v>36.28602953126413</v>
+        <v>35.81389089287329</v>
       </c>
       <c r="Q9">
-        <v>65.08602953126413</v>
+        <v>64.61389089287329</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09697096518559851</v>
+        <v>0.09747507951489312</v>
       </c>
       <c r="T9">
-        <v>1.025653426886941</v>
+        <v>1.035757723092973</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.97922957996757</v>
+        <v>10.48182588247163</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09340667315370167</v>
+        <v>0.09350464868479673</v>
       </c>
       <c r="C10">
-        <v>939.9958297067609</v>
+        <v>927.8207823582093</v>
       </c>
       <c r="D10">
-        <v>997.0149010737001</v>
+        <v>994.9672376460159</v>
       </c>
       <c r="E10">
-        <v>-110.1193207198007</v>
+        <v>-99.99193679893332</v>
       </c>
       <c r="F10">
-        <v>81.0190713669392</v>
+        <v>91.14645528780659</v>
       </c>
       <c r="G10">
         <v>24</v>
@@ -2107,45 +2107,45 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M10">
-        <v>4.19678789680745</v>
+        <v>4.876335357897652</v>
       </c>
       <c r="N10">
-        <v>39.79321210319254</v>
+        <v>39.11366464210234</v>
       </c>
       <c r="O10">
-        <v>3.979321210319255</v>
+        <v>3.911366464210234</v>
       </c>
       <c r="P10">
-        <v>35.81389089287329</v>
+        <v>35.20229817789211</v>
       </c>
       <c r="Q10">
-        <v>64.61389089287329</v>
+        <v>64.00229817789211</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09747507951489312</v>
+        <v>0.0979902732799964</v>
       </c>
       <c r="T10">
-        <v>1.035757723092973</v>
+        <v>1.046084091743094</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.1</v>
       </c>
       <c r="W10">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.48182588247163</v>
+        <v>9.021118682650556</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09350464868479673</v>
+        <v>0.09348022421589181</v>
       </c>
       <c r="C11">
-        <v>927.8207823582093</v>
+        <v>918.2030761235723</v>
       </c>
       <c r="D11">
-        <v>994.9672376460159</v>
+        <v>995.4769153322462</v>
       </c>
       <c r="E11">
-        <v>-99.99193679893332</v>
+        <v>-89.86455287806592</v>
       </c>
       <c r="F11">
-        <v>91.14645528780659</v>
+        <v>101.273839208674</v>
       </c>
       <c r="G11">
         <v>24</v>
@@ -2189,28 +2189,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M11">
-        <v>4.876335357897652</v>
+        <v>5.418150397664059</v>
       </c>
       <c r="N11">
-        <v>39.11366464210234</v>
+        <v>38.57184960233594</v>
       </c>
       <c r="O11">
-        <v>3.911366464210234</v>
+        <v>3.857184960233594</v>
       </c>
       <c r="P11">
-        <v>35.20229817789211</v>
+        <v>34.71466464210234</v>
       </c>
       <c r="Q11">
-        <v>64.00229817789211</v>
+        <v>63.51466464210235</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0979902732799964</v>
+        <v>0.09851691579543534</v>
       </c>
       <c r="T11">
-        <v>1.046084091743094</v>
+        <v>1.056639935252106</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>9.021118682650556</v>
+        <v>8.1190068143855</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09348022421589181</v>
+        <v>0.09353499974698684</v>
       </c>
       <c r="C12">
-        <v>918.2030761235723</v>
+        <v>906.9333903902154</v>
       </c>
       <c r="D12">
-        <v>995.4769153322462</v>
+        <v>994.3346135197568</v>
       </c>
       <c r="E12">
-        <v>-89.86455287806591</v>
+        <v>-79.73716895719852</v>
       </c>
       <c r="F12">
-        <v>101.273839208674</v>
+        <v>111.4012231295414</v>
       </c>
       <c r="G12">
         <v>24</v>
@@ -2271,45 +2271,45 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M12">
-        <v>5.418150397664059</v>
+        <v>6.049086415934098</v>
       </c>
       <c r="N12">
-        <v>38.57184960233594</v>
+        <v>37.9409135840659</v>
       </c>
       <c r="O12">
-        <v>3.857184960233594</v>
+        <v>3.79409135840659</v>
       </c>
       <c r="P12">
-        <v>34.71466464210234</v>
+        <v>34.14682222565931</v>
       </c>
       <c r="Q12">
-        <v>63.51466464210235</v>
+        <v>62.9468222256593</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09851691579543534</v>
+        <v>0.09905539297414252</v>
       </c>
       <c r="T12">
-        <v>1.056639935252106</v>
+        <v>1.067432988727612</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.1</v>
       </c>
       <c r="W12">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>8.1190068143855</v>
+        <v>7.272172519163305</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09353499974698684</v>
+        <v>0.09351777527808193</v>
       </c>
       <c r="C13">
-        <v>906.9333903902154</v>
+        <v>897.1649269247094</v>
       </c>
       <c r="D13">
-        <v>994.3346135197568</v>
+        <v>994.6935339751183</v>
       </c>
       <c r="E13">
-        <v>-79.73716895719852</v>
+        <v>-69.60978503633112</v>
       </c>
       <c r="F13">
-        <v>111.4012231295414</v>
+        <v>121.5286070504088</v>
       </c>
       <c r="G13">
         <v>24</v>
@@ -2353,28 +2353,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M13">
-        <v>6.049086415934098</v>
+        <v>6.599003362837197</v>
       </c>
       <c r="N13">
-        <v>37.9409135840659</v>
+        <v>37.3909966371628</v>
       </c>
       <c r="O13">
-        <v>3.79409135840659</v>
+        <v>3.73909966371628</v>
       </c>
       <c r="P13">
-        <v>34.14682222565931</v>
+        <v>33.65189697344652</v>
       </c>
       <c r="Q13">
-        <v>62.9468222256593</v>
+        <v>62.45189697344652</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09905539297414252</v>
+        <v>0.09960610827054764</v>
       </c>
       <c r="T13">
-        <v>1.067432988727612</v>
+        <v>1.078471338873017</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.272172519163305</v>
+        <v>6.666158142566363</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09351777527808193</v>
+        <v>0.09350055080917698</v>
       </c>
       <c r="C14">
-        <v>897.1649269247094</v>
+        <v>887.3967226685476</v>
       </c>
       <c r="D14">
-        <v>994.6935339751183</v>
+        <v>995.0527136398238</v>
       </c>
       <c r="E14">
-        <v>-69.60978503633112</v>
+        <v>-59.48240111546372</v>
       </c>
       <c r="F14">
-        <v>121.5286070504088</v>
+        <v>131.6559909712762</v>
       </c>
       <c r="G14">
         <v>24</v>
@@ -2435,28 +2435,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M14">
-        <v>6.599003362837197</v>
+        <v>7.148920309740298</v>
       </c>
       <c r="N14">
-        <v>37.3909966371628</v>
+        <v>36.8410796902597</v>
       </c>
       <c r="O14">
-        <v>3.73909966371628</v>
+        <v>3.68410796902597</v>
       </c>
       <c r="P14">
-        <v>33.65189697344652</v>
+        <v>33.15697172123373</v>
       </c>
       <c r="Q14">
-        <v>62.45189697344652</v>
+        <v>61.95697172123373</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09960610827054764</v>
+        <v>0.1001694836887092</v>
       </c>
       <c r="T14">
-        <v>1.078471338873017</v>
+        <v>1.089763444194178</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.666158142566363</v>
+        <v>6.153376746984335</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09350055080917698</v>
+        <v>0.09360932634027203</v>
       </c>
       <c r="C15">
-        <v>887.3967226685476</v>
+        <v>875.0053999792613</v>
       </c>
       <c r="D15">
-        <v>995.0527136398238</v>
+        <v>992.7887748714048</v>
       </c>
       <c r="E15">
-        <v>-59.48240111546372</v>
+        <v>-49.35501719459631</v>
       </c>
       <c r="F15">
-        <v>131.6559909712762</v>
+        <v>141.7833748921436</v>
       </c>
       <c r="G15">
         <v>24</v>
@@ -2517,45 +2517,45 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M15">
-        <v>7.148920309740298</v>
+        <v>7.840620631535542</v>
       </c>
       <c r="N15">
-        <v>36.8410796902597</v>
+        <v>36.14937936846445</v>
       </c>
       <c r="O15">
-        <v>3.68410796902597</v>
+        <v>3.614937936846445</v>
       </c>
       <c r="P15">
-        <v>33.15697172123373</v>
+        <v>32.53444143161801</v>
       </c>
       <c r="Q15">
-        <v>61.95697172123373</v>
+        <v>61.334441431618</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1001694836887092</v>
+        <v>0.1007459608607814</v>
       </c>
       <c r="T15">
-        <v>1.089763444194178</v>
+        <v>1.101318156615831</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.1</v>
       </c>
       <c r="W15">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.153376746984335</v>
+        <v>5.610525246313926</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09360932634027203</v>
+        <v>0.0936011018713671</v>
       </c>
       <c r="C16">
-        <v>875.0053999792613</v>
+        <v>865.0488313762093</v>
       </c>
       <c r="D16">
-        <v>992.7887748714048</v>
+        <v>992.9595901892203</v>
       </c>
       <c r="E16">
-        <v>-49.35501719459631</v>
+        <v>-39.22763327372888</v>
       </c>
       <c r="F16">
-        <v>141.7833748921436</v>
+        <v>151.910758813011</v>
       </c>
       <c r="G16">
         <v>24</v>
@@ -2599,28 +2599,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M16">
-        <v>7.840620631535542</v>
+        <v>8.40066496235951</v>
       </c>
       <c r="N16">
-        <v>36.14937936846445</v>
+        <v>35.58933503764048</v>
       </c>
       <c r="O16">
-        <v>3.614937936846445</v>
+        <v>3.558933503764048</v>
       </c>
       <c r="P16">
-        <v>32.53444143161801</v>
+        <v>32.03040153387644</v>
       </c>
       <c r="Q16">
-        <v>61.334441431618</v>
+        <v>60.83040153387644</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1007459608607814</v>
+        <v>0.1013360022016083</v>
       </c>
       <c r="T16">
-        <v>1.101318156615831</v>
+        <v>1.113144744623876</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.610525246313926</v>
+        <v>5.236490229892996</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0936011018713671</v>
+        <v>0.09359287740246215</v>
       </c>
       <c r="C17">
-        <v>865.0488313762094</v>
+        <v>855.0923215628916</v>
       </c>
       <c r="D17">
-        <v>992.9595901892203</v>
+        <v>993.13046429677</v>
       </c>
       <c r="E17">
-        <v>-39.22763327372891</v>
+        <v>-29.10024935286151</v>
       </c>
       <c r="F17">
-        <v>151.910758813011</v>
+        <v>162.0381427338784</v>
       </c>
       <c r="G17">
         <v>24</v>
@@ -2681,28 +2681,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M17">
-        <v>8.400664962359508</v>
+        <v>8.960709293183475</v>
       </c>
       <c r="N17">
-        <v>35.58933503764049</v>
+        <v>35.02929070681652</v>
       </c>
       <c r="O17">
-        <v>3.558933503764049</v>
+        <v>3.502929070681652</v>
       </c>
       <c r="P17">
-        <v>32.03040153387644</v>
+        <v>31.52636163613487</v>
       </c>
       <c r="Q17">
-        <v>60.83040153387644</v>
+        <v>60.32636163613486</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1013360022016083</v>
+        <v>0.1019400921457883</v>
       </c>
       <c r="T17">
-        <v>1.113144744623876</v>
+        <v>1.125252918060684</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.236490229892998</v>
+        <v>4.909209590524686</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09359287740246215</v>
+        <v>0.09358465293355719</v>
       </c>
       <c r="C18">
-        <v>855.0923215628916</v>
+        <v>845.1358705696639</v>
       </c>
       <c r="D18">
-        <v>993.13046429677</v>
+        <v>993.3013972244097</v>
       </c>
       <c r="E18">
-        <v>-29.10024935286151</v>
+        <v>-18.97286543199411</v>
       </c>
       <c r="F18">
-        <v>162.0381427338784</v>
+        <v>172.1655266547458</v>
       </c>
       <c r="G18">
         <v>24</v>
@@ -2763,28 +2763,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M18">
-        <v>8.960709293183475</v>
+        <v>9.520753624007444</v>
       </c>
       <c r="N18">
-        <v>35.02929070681652</v>
+        <v>34.46924637599255</v>
       </c>
       <c r="O18">
-        <v>3.502929070681652</v>
+        <v>3.446924637599256</v>
       </c>
       <c r="P18">
-        <v>31.52636163613487</v>
+        <v>31.0223217383933</v>
       </c>
       <c r="Q18">
-        <v>60.32636163613486</v>
+        <v>59.8223217383933</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1019400921457883</v>
+        <v>0.1025587384741653</v>
       </c>
       <c r="T18">
-        <v>1.125252918060684</v>
+        <v>1.137652854712837</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.909209590524686</v>
+        <v>4.620432555787939</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09358465293355719</v>
+        <v>0.09398142846465227</v>
       </c>
       <c r="C19">
-        <v>845.1358705696639</v>
+        <v>826.8286193849951</v>
       </c>
       <c r="D19">
-        <v>993.3013972244097</v>
+        <v>985.1215299606083</v>
       </c>
       <c r="E19">
-        <v>-18.97286543199411</v>
+        <v>-8.845481511126707</v>
       </c>
       <c r="F19">
-        <v>172.1655266547458</v>
+        <v>182.2929105756132</v>
       </c>
       <c r="G19">
         <v>24</v>
@@ -2845,45 +2845,45 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M19">
-        <v>9.520753624007444</v>
+        <v>10.53653023127044</v>
       </c>
       <c r="N19">
-        <v>34.46924637599255</v>
+        <v>33.45346976872955</v>
       </c>
       <c r="O19">
-        <v>3.446924637599256</v>
+        <v>3.345346976872955</v>
       </c>
       <c r="P19">
-        <v>31.0223217383933</v>
+        <v>30.10812279185659</v>
       </c>
       <c r="Q19">
-        <v>59.8223217383933</v>
+        <v>58.9081227918566</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1025587384741653</v>
+        <v>0.1031924737373808</v>
       </c>
       <c r="T19">
-        <v>1.137652854712837</v>
+        <v>1.15035522884431</v>
       </c>
       <c r="U19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V19">
         <v>0.1</v>
       </c>
       <c r="W19">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.620432555787939</v>
+        <v>4.174998698285506</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09398142846465228</v>
+        <v>0.09459420399574732</v>
       </c>
       <c r="C20">
-        <v>826.8286193849949</v>
+        <v>804.3297175525456</v>
       </c>
       <c r="D20">
-        <v>985.1215299606081</v>
+        <v>972.7500120490262</v>
       </c>
       <c r="E20">
-        <v>-8.845481511126735</v>
+        <v>1.281902409740695</v>
       </c>
       <c r="F20">
-        <v>182.2929105756132</v>
+        <v>192.4202944964806</v>
       </c>
       <c r="G20">
         <v>24</v>
@@ -2927,45 +2927,45 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M20">
-        <v>10.53653023127044</v>
+        <v>11.79536405263426</v>
       </c>
       <c r="N20">
-        <v>33.45346976872955</v>
+        <v>32.19463594736573</v>
       </c>
       <c r="O20">
-        <v>3.345346976872956</v>
+        <v>3.219463594736574</v>
       </c>
       <c r="P20">
-        <v>30.1081227918566</v>
+        <v>28.97517235262916</v>
       </c>
       <c r="Q20">
-        <v>58.9081227918566</v>
+        <v>57.77517235262916</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1031924737373808</v>
+        <v>0.1038418567848732</v>
       </c>
       <c r="T20">
-        <v>1.15035522884431</v>
+        <v>1.163371241843228</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.1</v>
       </c>
       <c r="W20">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.174998698285508</v>
+        <v>3.729431309089243</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09459420399574732</v>
+        <v>0.0946399795268424</v>
       </c>
       <c r="C21">
-        <v>804.3297175525456</v>
+        <v>793.2906184987957</v>
       </c>
       <c r="D21">
-        <v>972.7500120490262</v>
+        <v>971.8382969161437</v>
       </c>
       <c r="E21">
-        <v>1.281902409740695</v>
+        <v>11.4092863306081</v>
       </c>
       <c r="F21">
-        <v>192.4202944964806</v>
+        <v>202.547678417348</v>
       </c>
       <c r="G21">
         <v>24</v>
@@ -3009,28 +3009,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M21">
-        <v>11.79536405263426</v>
+        <v>12.41617268698343</v>
       </c>
       <c r="N21">
-        <v>32.19463594736573</v>
+        <v>31.57382731301656</v>
       </c>
       <c r="O21">
-        <v>3.219463594736574</v>
+        <v>3.157382731301656</v>
       </c>
       <c r="P21">
-        <v>28.97517235262916</v>
+        <v>28.41644458171491</v>
       </c>
       <c r="Q21">
-        <v>57.77517235262916</v>
+        <v>57.21644458171491</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1038418567848732</v>
+        <v>0.104507474408553</v>
       </c>
       <c r="T21">
-        <v>1.163371241843228</v>
+        <v>1.176712655167118</v>
       </c>
       <c r="U21">
         <v>0.0613</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.729431309089243</v>
+        <v>3.542959743634781</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0946399795268424</v>
+        <v>0.09521495505793744</v>
       </c>
       <c r="C22">
-        <v>793.2906184987957</v>
+        <v>771.8552562492482</v>
       </c>
       <c r="D22">
-        <v>971.8382969161437</v>
+        <v>960.5303185874636</v>
       </c>
       <c r="E22">
-        <v>11.4092863306081</v>
+        <v>21.5366702514755</v>
       </c>
       <c r="F22">
-        <v>202.547678417348</v>
+        <v>212.6750623382154</v>
       </c>
       <c r="G22">
         <v>24</v>
@@ -3091,45 +3091,45 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M22">
-        <v>12.41617268698343</v>
+        <v>13.63247149587961</v>
       </c>
       <c r="N22">
-        <v>31.57382731301656</v>
+        <v>30.35752850412039</v>
       </c>
       <c r="O22">
-        <v>3.157382731301656</v>
+        <v>3.035752850412039</v>
       </c>
       <c r="P22">
-        <v>28.41644458171491</v>
+        <v>27.32177565370835</v>
       </c>
       <c r="Q22">
-        <v>57.21644458171491</v>
+        <v>56.12177565370835</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.104507474408553</v>
+        <v>0.1051899431113132</v>
       </c>
       <c r="T22">
-        <v>1.176712655167118</v>
+        <v>1.190391825790347</v>
       </c>
       <c r="U22">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V22">
         <v>0.1</v>
       </c>
       <c r="W22">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.542959743634781</v>
+        <v>3.226854353834219</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09521495505793744</v>
+        <v>0.09528593058903251</v>
       </c>
       <c r="C23">
-        <v>771.8552562492482</v>
+        <v>760.350225213672</v>
       </c>
       <c r="D23">
-        <v>960.5303185874636</v>
+        <v>959.1526714727548</v>
       </c>
       <c r="E23">
-        <v>21.53667025147547</v>
+        <v>31.66405417234287</v>
       </c>
       <c r="F23">
-        <v>212.6750623382154</v>
+        <v>222.8024462590828</v>
       </c>
       <c r="G23">
         <v>24</v>
@@ -3173,28 +3173,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M23">
-        <v>13.63247149587961</v>
+        <v>14.28163680520721</v>
       </c>
       <c r="N23">
-        <v>30.35752850412039</v>
+        <v>29.70836319479279</v>
       </c>
       <c r="O23">
-        <v>3.035752850412039</v>
+        <v>2.970836319479279</v>
       </c>
       <c r="P23">
-        <v>27.32177565370835</v>
+        <v>26.73752687531351</v>
       </c>
       <c r="Q23">
-        <v>56.12177565370835</v>
+        <v>55.53752687531351</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1051899431113132</v>
+        <v>0.1058899110115801</v>
       </c>
       <c r="T23">
-        <v>1.190391825790347</v>
+        <v>1.204421744378275</v>
       </c>
       <c r="U23">
         <v>0.0641</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.226854353834219</v>
+        <v>3.080179155932663</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09528593058903251</v>
+        <v>0.09697150612012757</v>
       </c>
       <c r="C24">
-        <v>760.350225213672</v>
+        <v>718.6286124689823</v>
       </c>
       <c r="D24">
-        <v>959.1526714727548</v>
+        <v>927.5584426489324</v>
       </c>
       <c r="E24">
-        <v>31.66405417234287</v>
+        <v>41.7914380932103</v>
       </c>
       <c r="F24">
-        <v>222.8024462590828</v>
+        <v>232.9298301799502</v>
       </c>
       <c r="G24">
         <v>24</v>
@@ -3255,45 +3255,45 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M24">
-        <v>14.28163680520721</v>
+        <v>16.74765478993842</v>
       </c>
       <c r="N24">
-        <v>29.70836319479279</v>
+        <v>27.24234521006157</v>
       </c>
       <c r="O24">
-        <v>2.970836319479279</v>
+        <v>2.724234521006157</v>
       </c>
       <c r="P24">
-        <v>26.73752687531351</v>
+        <v>24.51811068905542</v>
       </c>
       <c r="Q24">
-        <v>55.53752687531351</v>
+        <v>53.31811068905542</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1058899110115801</v>
+        <v>0.1066080598962696</v>
       </c>
       <c r="T24">
-        <v>1.204421744378275</v>
+        <v>1.218816076436018</v>
       </c>
       <c r="U24">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V24">
         <v>0.1</v>
       </c>
       <c r="W24">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.080179155932663</v>
+        <v>2.626636418755663</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09697150612012757</v>
+        <v>0.09711268165122262</v>
       </c>
       <c r="C25">
-        <v>718.6286124689823</v>
+        <v>705.949255984047</v>
       </c>
       <c r="D25">
-        <v>927.5584426489324</v>
+        <v>925.0064700848646</v>
       </c>
       <c r="E25">
-        <v>41.7914380932103</v>
+        <v>51.9188220140777</v>
       </c>
       <c r="F25">
-        <v>232.9298301799502</v>
+        <v>243.0572141008176</v>
       </c>
       <c r="G25">
         <v>24</v>
@@ -3337,28 +3337,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M25">
-        <v>16.74765478993842</v>
+        <v>17.47581369384879</v>
       </c>
       <c r="N25">
-        <v>27.24234521006157</v>
+        <v>26.51418630615121</v>
       </c>
       <c r="O25">
-        <v>2.724234521006157</v>
+        <v>2.651418630615121</v>
       </c>
       <c r="P25">
-        <v>24.51811068905542</v>
+        <v>23.86276767553608</v>
       </c>
       <c r="Q25">
-        <v>53.31811068905542</v>
+        <v>52.66276767553609</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1066080598962696</v>
+        <v>0.1073451074358192</v>
       </c>
       <c r="T25">
-        <v>1.218816076436018</v>
+        <v>1.233589206705808</v>
       </c>
       <c r="U25">
         <v>0.07190000000000001</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.626636418755663</v>
+        <v>2.517193234640844</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09711268165122262</v>
+        <v>0.09813135718231768</v>
       </c>
       <c r="C26">
-        <v>705.9492559840471</v>
+        <v>677.8158139764911</v>
       </c>
       <c r="D26">
-        <v>925.0064700848646</v>
+        <v>907.0004119981761</v>
       </c>
       <c r="E26">
-        <v>51.91882201407768</v>
+        <v>62.04620593494508</v>
       </c>
       <c r="F26">
-        <v>243.0572141008176</v>
+        <v>253.184598021685</v>
       </c>
       <c r="G26">
         <v>24</v>
@@ -3419,45 +3419,45 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M26">
-        <v>17.47581369384879</v>
+        <v>19.19139253004372</v>
       </c>
       <c r="N26">
-        <v>26.51418630615121</v>
+        <v>24.79860746995627</v>
       </c>
       <c r="O26">
-        <v>2.651418630615121</v>
+        <v>2.479860746995627</v>
       </c>
       <c r="P26">
-        <v>23.86276767553609</v>
+        <v>22.31874672296064</v>
       </c>
       <c r="Q26">
-        <v>52.66276767553609</v>
+        <v>51.11874672296064</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1073451074358192</v>
+        <v>0.1081018095764236</v>
       </c>
       <c r="T26">
-        <v>1.233589206705808</v>
+        <v>1.248756287116125</v>
       </c>
       <c r="U26">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V26">
         <v>0.1</v>
       </c>
       <c r="W26">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.517193234640845</v>
+        <v>2.292173427808043</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09813135718231768</v>
+        <v>0.09830763271341275</v>
       </c>
       <c r="C27">
-        <v>677.8158139764911</v>
+        <v>664.6435017077572</v>
       </c>
       <c r="D27">
-        <v>907.0004119981761</v>
+        <v>903.9554836503096</v>
       </c>
       <c r="E27">
-        <v>62.04620593494508</v>
+        <v>72.17358985581248</v>
       </c>
       <c r="F27">
-        <v>253.184598021685</v>
+        <v>263.3119819425524</v>
       </c>
       <c r="G27">
         <v>24</v>
@@ -3501,28 +3501,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M27">
-        <v>19.19139253004372</v>
+        <v>19.95904823124547</v>
       </c>
       <c r="N27">
-        <v>24.79860746995627</v>
+        <v>24.03095176875452</v>
       </c>
       <c r="O27">
-        <v>2.479860746995627</v>
+        <v>2.403095176875452</v>
       </c>
       <c r="P27">
-        <v>22.31874672296064</v>
+        <v>21.62785659187907</v>
       </c>
       <c r="Q27">
-        <v>51.11874672296064</v>
+        <v>50.42785659187907</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1081018095764236</v>
+        <v>0.1088789631262334</v>
       </c>
       <c r="T27">
-        <v>1.248756287116125</v>
+        <v>1.264333288618613</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.292173427808043</v>
+        <v>2.204012911353888</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09830763271341275</v>
+        <v>0.09848390824450781</v>
       </c>
       <c r="C28">
-        <v>664.6435017077572</v>
+        <v>651.4915655416914</v>
       </c>
       <c r="D28">
-        <v>903.9554836503096</v>
+        <v>900.9309314051113</v>
       </c>
       <c r="E28">
-        <v>72.17358985581248</v>
+        <v>82.30097377667991</v>
       </c>
       <c r="F28">
-        <v>263.3119819425524</v>
+        <v>273.4393658634198</v>
       </c>
       <c r="G28">
         <v>24</v>
@@ -3583,28 +3583,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M28">
-        <v>19.95904823124547</v>
+        <v>20.72670393244723</v>
       </c>
       <c r="N28">
-        <v>24.03095176875452</v>
+        <v>23.26329606755277</v>
       </c>
       <c r="O28">
-        <v>2.403095176875452</v>
+        <v>2.326329606755277</v>
       </c>
       <c r="P28">
-        <v>21.62785659187907</v>
+        <v>20.93696646079749</v>
       </c>
       <c r="Q28">
-        <v>50.42785659187907</v>
+        <v>49.73696646079749</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1088789631262334</v>
+        <v>0.1096774085541203</v>
       </c>
       <c r="T28">
-        <v>1.264333288618613</v>
+        <v>1.280337057285553</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.204012911353888</v>
+        <v>2.122382803525965</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09848390824450781</v>
+        <v>0.09866018377560284</v>
       </c>
       <c r="C29">
-        <v>651.4915655416914</v>
+        <v>638.3598016306305</v>
       </c>
       <c r="D29">
-        <v>900.9309314051113</v>
+        <v>897.9265514149178</v>
       </c>
       <c r="E29">
-        <v>82.30097377667991</v>
+        <v>92.42835769754728</v>
       </c>
       <c r="F29">
-        <v>273.4393658634198</v>
+        <v>283.5667497842872</v>
       </c>
       <c r="G29">
         <v>24</v>
@@ -3665,28 +3665,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M29">
-        <v>20.72670393244723</v>
+        <v>21.49435963364897</v>
       </c>
       <c r="N29">
-        <v>23.26329606755277</v>
+        <v>22.49564036635102</v>
       </c>
       <c r="O29">
-        <v>2.326329606755277</v>
+        <v>2.249564036635102</v>
       </c>
       <c r="P29">
-        <v>20.93696646079749</v>
+        <v>20.24607632971592</v>
       </c>
       <c r="Q29">
-        <v>49.73696646079749</v>
+        <v>49.04607632971592</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1096774085541203</v>
+        <v>0.1104980330216706</v>
       </c>
       <c r="T29">
-        <v>1.280337057285553</v>
+        <v>1.29678537508213</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.122382803525965</v>
+        <v>2.046583417685753</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09866018377560284</v>
+        <v>0.1025426593066979</v>
       </c>
       <c r="C30">
-        <v>638.3598016306305</v>
+        <v>566.7940236128989</v>
       </c>
       <c r="D30">
-        <v>897.9265514149178</v>
+        <v>836.4881573180535</v>
       </c>
       <c r="E30">
-        <v>92.42835769754728</v>
+        <v>102.5557416184147</v>
       </c>
       <c r="F30">
-        <v>283.5667497842872</v>
+        <v>293.6941337051546</v>
       </c>
       <c r="G30">
         <v>24</v>
@@ -3747,45 +3747,45 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M30">
-        <v>21.49435963364897</v>
+        <v>26.43247203346392</v>
       </c>
       <c r="N30">
-        <v>22.49564036635102</v>
+        <v>17.55752796653608</v>
       </c>
       <c r="O30">
-        <v>2.249564036635102</v>
+        <v>1.755752796653608</v>
       </c>
       <c r="P30">
-        <v>20.24607632971592</v>
+        <v>15.80177516988247</v>
       </c>
       <c r="Q30">
-        <v>49.04607632971592</v>
+        <v>44.60177516988247</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1104980330216706</v>
+        <v>0.1113417736714055</v>
       </c>
       <c r="T30">
-        <v>1.29678537508213</v>
+        <v>1.313697025774385</v>
       </c>
       <c r="U30">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V30">
         <v>0.1</v>
       </c>
       <c r="W30">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.046583417685753</v>
+        <v>1.664240860420016</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1025426593066979</v>
+        <v>0.102846734837793</v>
       </c>
       <c r="C31">
-        <v>566.7940236128991</v>
+        <v>552.2079168323545</v>
       </c>
       <c r="D31">
-        <v>836.4881573180537</v>
+        <v>832.0294344583765</v>
       </c>
       <c r="E31">
-        <v>102.5557416184147</v>
+        <v>112.6831255392821</v>
       </c>
       <c r="F31">
-        <v>293.6941337051546</v>
+        <v>303.821517626022</v>
       </c>
       <c r="G31">
         <v>24</v>
@@ -3829,28 +3829,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M31">
-        <v>26.43247203346391</v>
+        <v>27.34393658634198</v>
       </c>
       <c r="N31">
-        <v>17.55752796653609</v>
+        <v>16.64606341365802</v>
       </c>
       <c r="O31">
-        <v>1.755752796653609</v>
+        <v>1.664606341365802</v>
       </c>
       <c r="P31">
-        <v>15.80177516988248</v>
+        <v>14.98145707229221</v>
       </c>
       <c r="Q31">
-        <v>44.60177516988248</v>
+        <v>43.78145707229221</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1113417736714055</v>
+        <v>0.1122096211968471</v>
       </c>
       <c r="T31">
-        <v>1.313697025774385</v>
+        <v>1.331091866486419</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.664240860420016</v>
+        <v>1.608766165072682</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.102846734837793</v>
+        <v>0.103150810368888</v>
       </c>
       <c r="C32">
-        <v>552.2079168323545</v>
+        <v>537.6690905876156</v>
       </c>
       <c r="D32">
-        <v>832.0294344583765</v>
+        <v>827.617992134505</v>
       </c>
       <c r="E32">
-        <v>112.6831255392821</v>
+        <v>122.8105094601495</v>
       </c>
       <c r="F32">
-        <v>303.821517626022</v>
+        <v>313.9489015468894</v>
       </c>
       <c r="G32">
         <v>24</v>
@@ -3911,28 +3911,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M32">
-        <v>27.34393658634198</v>
+        <v>28.25540113922004</v>
       </c>
       <c r="N32">
-        <v>16.64606341365802</v>
+        <v>15.73459886077995</v>
       </c>
       <c r="O32">
-        <v>1.664606341365802</v>
+        <v>1.573459886077995</v>
       </c>
       <c r="P32">
-        <v>14.98145707229221</v>
+        <v>14.16113897470196</v>
       </c>
       <c r="Q32">
-        <v>43.78145707229221</v>
+        <v>42.96113897470195</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1122096211968471</v>
+        <v>0.1131026237230261</v>
       </c>
       <c r="T32">
-        <v>1.331091866486419</v>
+        <v>1.348990905479961</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.608766165072682</v>
+        <v>1.556870482328402</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.103150810368888</v>
+        <v>0.1034548858999831</v>
       </c>
       <c r="C33">
-        <v>537.6690905876156</v>
+        <v>523.1767967970331</v>
       </c>
       <c r="D33">
-        <v>827.617992134505</v>
+        <v>823.2530822647899</v>
       </c>
       <c r="E33">
-        <v>122.8105094601495</v>
+        <v>132.9378933810169</v>
       </c>
       <c r="F33">
-        <v>313.9489015468894</v>
+        <v>324.0762854677568</v>
       </c>
       <c r="G33">
         <v>24</v>
@@ -3993,28 +3993,28 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M33">
-        <v>28.25540113922004</v>
+        <v>29.16686569209811</v>
       </c>
       <c r="N33">
-        <v>15.73459886077995</v>
+        <v>14.82313430790188</v>
       </c>
       <c r="O33">
-        <v>1.573459886077995</v>
+        <v>1.482313430790189</v>
       </c>
       <c r="P33">
-        <v>14.16113897470196</v>
+        <v>13.3408208771117</v>
       </c>
       <c r="Q33">
-        <v>42.96113897470195</v>
+        <v>42.14082087711169</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1131026237230261</v>
+        <v>0.1140218910293869</v>
       </c>
       <c r="T33">
-        <v>1.348990905479961</v>
+        <v>1.367416386796843</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.556870482328402</v>
+        <v>1.50821827975564</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1034548858999831</v>
+        <v>0.1212927620239314</v>
       </c>
       <c r="C34">
-        <v>523.1767967970331</v>
+        <v>318.5263075294211</v>
       </c>
       <c r="D34">
-        <v>823.2530822647899</v>
+        <v>628.7299769180453</v>
       </c>
       <c r="E34">
-        <v>132.9378933810169</v>
+        <v>143.0652773018843</v>
       </c>
       <c r="F34">
-        <v>324.0762854677568</v>
+        <v>334.2036693886242</v>
       </c>
       <c r="G34">
         <v>24</v>
@@ -4075,45 +4075,45 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M34">
-        <v>29.16686569209811</v>
+        <v>49.06109866625003</v>
       </c>
       <c r="N34">
-        <v>14.82313430790188</v>
+        <v>-5.071098666250037</v>
       </c>
       <c r="O34">
-        <v>1.482313430790189</v>
+        <v>-0.5071098666250038</v>
       </c>
       <c r="P34">
-        <v>13.3408208771117</v>
+        <v>-4.563988799625034</v>
       </c>
       <c r="Q34">
-        <v>42.14082087711169</v>
+        <v>24.23601120037497</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1140218910293869</v>
+        <v>0.1152125830889964</v>
       </c>
       <c r="T34">
-        <v>1.367416386796843</v>
+        <v>1.391282213577247</v>
       </c>
       <c r="U34">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.1</v>
+        <v>0.0896637074910462</v>
       </c>
       <c r="W34">
-        <v>0.081</v>
+        <v>0.1336373677403144</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.50821827975564</v>
+        <v>0.896637074910462</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1212927620239314</v>
+        <v>0.1223027620239314</v>
       </c>
       <c r="C35">
-        <v>318.5263075294211</v>
+        <v>300.0983438662354</v>
       </c>
       <c r="D35">
-        <v>628.7299769180453</v>
+        <v>620.429397175727</v>
       </c>
       <c r="E35">
-        <v>143.0652773018843</v>
+        <v>153.1926612227517</v>
       </c>
       <c r="F35">
-        <v>334.2036693886242</v>
+        <v>344.3310533094916</v>
       </c>
       <c r="G35">
         <v>24</v>
@@ -4157,37 +4157,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M35">
-        <v>49.06109866625003</v>
+        <v>50.54779862583337</v>
       </c>
       <c r="N35">
-        <v>-5.071098666250037</v>
+        <v>-6.557798625833378</v>
       </c>
       <c r="O35">
-        <v>-0.5071098666250038</v>
+        <v>-0.6557798625833379</v>
       </c>
       <c r="P35">
-        <v>-4.563988799625034</v>
+        <v>-5.90201876325004</v>
       </c>
       <c r="Q35">
-        <v>24.23601120037497</v>
+        <v>22.89798123674996</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1152125830889964</v>
+        <v>0.1162642888933752</v>
       </c>
       <c r="T35">
-        <v>1.391282213577247</v>
+        <v>1.412362247116296</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.0896637074910462</v>
+        <v>0.08702653962366247</v>
       </c>
       <c r="W35">
-        <v>0.1336373677403144</v>
+        <v>0.1340245039832464</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.896637074910462</v>
+        <v>0.8702653962366247</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1223027620239314</v>
+        <v>0.1233127620239313</v>
       </c>
       <c r="C36">
-        <v>300.0983438662354</v>
+        <v>281.8866951767612</v>
       </c>
       <c r="D36">
-        <v>620.429397175727</v>
+        <v>612.3451324071202</v>
       </c>
       <c r="E36">
-        <v>153.1926612227517</v>
+        <v>163.3200451436191</v>
       </c>
       <c r="F36">
-        <v>344.3310533094916</v>
+        <v>354.458437230359</v>
       </c>
       <c r="G36">
         <v>24</v>
@@ -4239,37 +4239,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M36">
-        <v>50.54779862583337</v>
+        <v>52.03449858541671</v>
       </c>
       <c r="N36">
-        <v>-6.557798625833378</v>
+        <v>-8.044498585416719</v>
       </c>
       <c r="O36">
-        <v>-0.6557798625833379</v>
+        <v>-0.8044498585416719</v>
       </c>
       <c r="P36">
-        <v>-5.90201876325004</v>
+        <v>-7.240048726875047</v>
       </c>
       <c r="Q36">
-        <v>22.89798123674996</v>
+        <v>21.55995127312495</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1162642888933752</v>
+        <v>0.1173483548763501</v>
       </c>
       <c r="T36">
-        <v>1.412362247116296</v>
+        <v>1.434090897071931</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.08702653962366247</v>
+        <v>0.08454006706298639</v>
       </c>
       <c r="W36">
-        <v>0.1340245039832464</v>
+        <v>0.1343895181551536</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8702653962366247</v>
+        <v>0.8454006706298639</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1233127620239313</v>
+        <v>0.1243227620239314</v>
       </c>
       <c r="C37">
-        <v>281.8866951767612</v>
+        <v>263.8830143989047</v>
       </c>
       <c r="D37">
-        <v>612.3451324071202</v>
+        <v>604.4688355501311</v>
       </c>
       <c r="E37">
-        <v>163.3200451436191</v>
+        <v>173.4474290644865</v>
       </c>
       <c r="F37">
-        <v>354.458437230359</v>
+        <v>364.5858211512264</v>
       </c>
       <c r="G37">
         <v>24</v>
@@ -4321,37 +4321,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M37">
-        <v>52.03449858541671</v>
+        <v>53.52119854500004</v>
       </c>
       <c r="N37">
-        <v>-8.044498585416719</v>
+        <v>-9.531198545000045</v>
       </c>
       <c r="O37">
-        <v>-0.8044498585416719</v>
+        <v>-0.9531198545000046</v>
       </c>
       <c r="P37">
-        <v>-7.240048726875047</v>
+        <v>-8.578078690500041</v>
       </c>
       <c r="Q37">
-        <v>21.55995127312495</v>
+        <v>20.22192130949996</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1173483548763501</v>
+        <v>0.1184662979212932</v>
       </c>
       <c r="T37">
-        <v>1.434090897071931</v>
+        <v>1.456498567338681</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.08454006706298639</v>
+        <v>0.08219173186679235</v>
       </c>
       <c r="W37">
-        <v>0.1343895181551536</v>
+        <v>0.1347342537619549</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8454006706298639</v>
+        <v>0.8219173186679234</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1243227620239314</v>
+        <v>0.145694106967691</v>
       </c>
       <c r="C38">
-        <v>263.8830143989047</v>
+        <v>124.4355696212664</v>
       </c>
       <c r="D38">
-        <v>604.4688355501311</v>
+        <v>475.1487746933602</v>
       </c>
       <c r="E38">
-        <v>173.4474290644864</v>
+        <v>183.5748129853539</v>
       </c>
       <c r="F38">
-        <v>364.5858211512264</v>
+        <v>374.7132050720938</v>
       </c>
       <c r="G38">
         <v>24</v>
@@ -4403,45 +4403,45 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M38">
-        <v>53.52119854500003</v>
+        <v>75.24241157847644</v>
       </c>
       <c r="N38">
-        <v>-9.531198545000038</v>
+        <v>-31.25241157847644</v>
       </c>
       <c r="O38">
-        <v>-0.9531198545000038</v>
+        <v>-3.125241157847644</v>
       </c>
       <c r="P38">
-        <v>-8.578078690500034</v>
+        <v>-28.1271704206288</v>
       </c>
       <c r="Q38">
-        <v>20.22192130949997</v>
+        <v>0.6728295793712036</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1184662979212931</v>
+        <v>0.1202250406561702</v>
       </c>
       <c r="T38">
-        <v>1.45649856733868</v>
+        <v>1.491750208703985</v>
       </c>
       <c r="U38">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.08219173186679235</v>
+        <v>0.0584643674719533</v>
       </c>
       <c r="W38">
-        <v>0.1347342537619549</v>
+        <v>0.1890603550116318</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.8219173186679235</v>
+        <v>0.5846436747195329</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.145694106967691</v>
+        <v>0.147244106967691</v>
       </c>
       <c r="C39">
-        <v>124.4355696212664</v>
+        <v>107.0482213437779</v>
       </c>
       <c r="D39">
-        <v>475.1487746933602</v>
+        <v>467.8888103367391</v>
       </c>
       <c r="E39">
-        <v>183.5748129853539</v>
+        <v>193.7021969062213</v>
       </c>
       <c r="F39">
-        <v>374.7132050720938</v>
+        <v>384.8405889929612</v>
       </c>
       <c r="G39">
         <v>24</v>
@@ -4485,37 +4485,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M39">
-        <v>75.24241157847644</v>
+        <v>77.27599026978662</v>
       </c>
       <c r="N39">
-        <v>-31.25241157847644</v>
+        <v>-33.28599026978662</v>
       </c>
       <c r="O39">
-        <v>-3.125241157847644</v>
+        <v>-3.328599026978663</v>
       </c>
       <c r="P39">
-        <v>-28.1271704206288</v>
+        <v>-29.95739124280796</v>
       </c>
       <c r="Q39">
-        <v>0.6728295793712036</v>
+        <v>-1.157391242807961</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1202250406561702</v>
+        <v>0.1214254445377214</v>
       </c>
       <c r="T39">
-        <v>1.491750208703985</v>
+        <v>1.515810695941146</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.0584643674719533</v>
+        <v>0.05692583148584926</v>
       </c>
       <c r="W39">
-        <v>0.1890603550116318</v>
+        <v>0.1893692930376415</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5846436747195329</v>
+        <v>0.5692583148584925</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.147244106967691</v>
+        <v>0.148794106967691</v>
       </c>
       <c r="C40">
-        <v>107.0482213437779</v>
+        <v>89.87938935006639</v>
       </c>
       <c r="D40">
-        <v>467.8888103367391</v>
+        <v>460.847362263895</v>
       </c>
       <c r="E40">
-        <v>193.7021969062213</v>
+        <v>203.8295808270887</v>
       </c>
       <c r="F40">
-        <v>384.8405889929612</v>
+        <v>394.9679729138286</v>
       </c>
       <c r="G40">
         <v>24</v>
@@ -4567,37 +4567,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M40">
-        <v>77.27599026978662</v>
+        <v>79.30956896109679</v>
       </c>
       <c r="N40">
-        <v>-33.28599026978662</v>
+        <v>-35.31956896109679</v>
       </c>
       <c r="O40">
-        <v>-3.328599026978663</v>
+        <v>-3.531956896109679</v>
       </c>
       <c r="P40">
-        <v>-29.95739124280796</v>
+        <v>-31.78761206498711</v>
       </c>
       <c r="Q40">
-        <v>-1.157391242807961</v>
+        <v>-2.987612064987111</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1214254445377214</v>
+        <v>0.1226652059235856</v>
       </c>
       <c r="T40">
-        <v>1.515810695941146</v>
+        <v>1.540660051612312</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.05692583148584926</v>
+        <v>0.05546619478108389</v>
       </c>
       <c r="W40">
-        <v>0.1893692930376415</v>
+        <v>0.1896623880879584</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5692583148584925</v>
+        <v>0.5546619478108389</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.148794106967691</v>
+        <v>0.150344106967691</v>
       </c>
       <c r="C41">
-        <v>89.87938935006639</v>
+        <v>72.91935429057679</v>
       </c>
       <c r="D41">
-        <v>460.847362263895</v>
+        <v>454.0147111252728</v>
       </c>
       <c r="E41">
-        <v>203.8295808270887</v>
+        <v>213.9569647479561</v>
       </c>
       <c r="F41">
-        <v>394.9679729138286</v>
+        <v>405.095356834696</v>
       </c>
       <c r="G41">
         <v>24</v>
@@ -4649,37 +4649,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M41">
-        <v>79.30956896109679</v>
+        <v>81.34314765240697</v>
       </c>
       <c r="N41">
-        <v>-35.31956896109679</v>
+        <v>-37.35314765240697</v>
       </c>
       <c r="O41">
-        <v>-3.531956896109679</v>
+        <v>-3.735314765240698</v>
       </c>
       <c r="P41">
-        <v>-31.78761206498711</v>
+        <v>-33.61783288716628</v>
       </c>
       <c r="Q41">
-        <v>-2.987612064987111</v>
+        <v>-4.817832887166279</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1226652059235856</v>
+        <v>0.1239462926889787</v>
       </c>
       <c r="T41">
-        <v>1.540660051612312</v>
+        <v>1.566337719139184</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.05546619478108389</v>
+        <v>0.05407953991155678</v>
       </c>
       <c r="W41">
-        <v>0.1896623880879584</v>
+        <v>0.1899408283857594</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5546619478108389</v>
+        <v>0.5407953991155678</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.150344106967691</v>
+        <v>0.151894106967691</v>
       </c>
       <c r="C42">
-        <v>72.91935429057679</v>
+        <v>56.15896480175178</v>
       </c>
       <c r="D42">
-        <v>454.0147111252728</v>
+        <v>447.3817055573152</v>
       </c>
       <c r="E42">
-        <v>213.9569647479561</v>
+        <v>224.0843486688235</v>
       </c>
       <c r="F42">
-        <v>405.095356834696</v>
+        <v>415.2227407555634</v>
       </c>
       <c r="G42">
         <v>24</v>
@@ -4731,37 +4731,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M42">
-        <v>81.34314765240697</v>
+        <v>83.37672634371714</v>
       </c>
       <c r="N42">
-        <v>-37.35314765240697</v>
+        <v>-39.38672634371714</v>
       </c>
       <c r="O42">
-        <v>-3.735314765240698</v>
+        <v>-3.938672634371715</v>
       </c>
       <c r="P42">
-        <v>-33.61783288716628</v>
+        <v>-35.44805370934543</v>
       </c>
       <c r="Q42">
-        <v>-4.817832887166279</v>
+        <v>-6.648053709345429</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1239462926889787</v>
+        <v>0.1252708061243852</v>
       </c>
       <c r="T42">
-        <v>1.566337719139184</v>
+        <v>1.592885816073747</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.05407953991155678</v>
+        <v>0.05276052674298224</v>
       </c>
       <c r="W42">
-        <v>0.1899408283857594</v>
+        <v>0.1902056862300092</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5407953991155678</v>
+        <v>0.5276052674298224</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.151894106967691</v>
+        <v>0.153444106967691</v>
       </c>
       <c r="C43">
-        <v>56.15896480175178</v>
+        <v>39.5895966130231</v>
       </c>
       <c r="D43">
-        <v>447.3817055573152</v>
+        <v>440.9397212894539</v>
       </c>
       <c r="E43">
-        <v>224.0843486688235</v>
+        <v>234.2117325896909</v>
       </c>
       <c r="F43">
-        <v>415.2227407555634</v>
+        <v>425.3501246764308</v>
       </c>
       <c r="G43">
         <v>24</v>
@@ -4813,37 +4813,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M43">
-        <v>83.37672634371714</v>
+        <v>85.41030503502731</v>
       </c>
       <c r="N43">
-        <v>-39.38672634371714</v>
+        <v>-41.42030503502731</v>
       </c>
       <c r="O43">
-        <v>-3.938672634371715</v>
+        <v>-4.142030503502731</v>
       </c>
       <c r="P43">
-        <v>-35.44805370934543</v>
+        <v>-37.27827453152458</v>
       </c>
       <c r="Q43">
-        <v>-6.648053709345429</v>
+        <v>-8.47827453152458</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1252708061243852</v>
+        <v>0.1266409924368745</v>
       </c>
       <c r="T43">
-        <v>1.592885816073747</v>
+        <v>1.620349364626742</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.05276052674298224</v>
+        <v>0.05150432372529219</v>
       </c>
       <c r="W43">
-        <v>0.1902056862300092</v>
+        <v>0.1904579317959613</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5276052674298224</v>
+        <v>0.5150432372529219</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.153444106967691</v>
+        <v>0.154994106967691</v>
       </c>
       <c r="C44">
-        <v>39.58959661302316</v>
+        <v>23.20311513663592</v>
       </c>
       <c r="D44">
-        <v>440.9397212894539</v>
+        <v>434.6806237339341</v>
       </c>
       <c r="E44">
-        <v>234.2117325896909</v>
+        <v>244.3391165105583</v>
       </c>
       <c r="F44">
-        <v>425.3501246764308</v>
+        <v>435.4775085972982</v>
       </c>
       <c r="G44">
         <v>24</v>
@@ -4895,37 +4895,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M44">
-        <v>85.41030503502731</v>
+        <v>87.44388372633748</v>
       </c>
       <c r="N44">
-        <v>-41.42030503502731</v>
+        <v>-43.45388372633748</v>
       </c>
       <c r="O44">
-        <v>-4.142030503502731</v>
+        <v>-4.345388372633749</v>
       </c>
       <c r="P44">
-        <v>-37.27827453152458</v>
+        <v>-39.10849535370373</v>
       </c>
       <c r="Q44">
-        <v>-8.47827453152458</v>
+        <v>-10.30849535370373</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1266409924368745</v>
+        <v>0.1280592554620829</v>
       </c>
       <c r="T44">
-        <v>1.620349364626742</v>
+        <v>1.648776546462299</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.05150432372529219</v>
+        <v>0.05030654875493656</v>
       </c>
       <c r="W44">
-        <v>0.1904579317959613</v>
+        <v>0.1906984450100087</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5150432372529219</v>
+        <v>0.5030654875493656</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.154994106967691</v>
+        <v>0.1720979842586341</v>
       </c>
       <c r="C45">
-        <v>23.20311513663592</v>
+        <v>-45.79079854507813</v>
       </c>
       <c r="D45">
-        <v>434.6806237339341</v>
+        <v>375.8140939730874</v>
       </c>
       <c r="E45">
-        <v>244.3391165105583</v>
+        <v>254.4665004314257</v>
       </c>
       <c r="F45">
-        <v>435.4775085972982</v>
+        <v>445.6048925181656</v>
       </c>
       <c r="G45">
         <v>24</v>
@@ -4977,45 +4977,45 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M45">
-        <v>87.44388372633748</v>
+        <v>105.0736336557834</v>
       </c>
       <c r="N45">
-        <v>-43.45388372633748</v>
+        <v>-61.08363365578344</v>
       </c>
       <c r="O45">
-        <v>-4.345388372633749</v>
+        <v>-6.108363365578345</v>
       </c>
       <c r="P45">
-        <v>-39.10849535370373</v>
+        <v>-54.9752702902051</v>
       </c>
       <c r="Q45">
-        <v>-10.30849535370373</v>
+        <v>-26.1752702902051</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1280592554620829</v>
+        <v>0.1298029516148756</v>
       </c>
       <c r="T45">
-        <v>1.648776546462299</v>
+        <v>1.683726599252486</v>
       </c>
       <c r="U45">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.05030654875493656</v>
+        <v>0.04186587868856738</v>
       </c>
       <c r="W45">
-        <v>0.1906984450100087</v>
+        <v>0.2259280258052358</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.5030654875493656</v>
+        <v>0.4186587868856737</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1720979842586341</v>
+        <v>0.1739979842586341</v>
       </c>
       <c r="C46">
-        <v>-45.79079854507813</v>
+        <v>-61.48805770757423</v>
       </c>
       <c r="D46">
-        <v>375.8140939730874</v>
+        <v>370.2442187314588</v>
       </c>
       <c r="E46">
-        <v>254.4665004314257</v>
+        <v>264.5938843522931</v>
       </c>
       <c r="F46">
-        <v>445.6048925181656</v>
+        <v>455.732276439033</v>
       </c>
       <c r="G46">
         <v>24</v>
@@ -5059,37 +5059,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M46">
-        <v>105.0736336557834</v>
+        <v>107.461670784324</v>
       </c>
       <c r="N46">
-        <v>-61.08363365578344</v>
+        <v>-63.47167078432399</v>
       </c>
       <c r="O46">
-        <v>-6.108363365578345</v>
+        <v>-6.347167078432399</v>
       </c>
       <c r="P46">
-        <v>-54.9752702902051</v>
+        <v>-57.12450370589159</v>
       </c>
       <c r="Q46">
-        <v>-26.1752702902051</v>
+        <v>-28.32450370589159</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1298029516148756</v>
+        <v>0.1313302780078734</v>
       </c>
       <c r="T46">
-        <v>1.683726599252486</v>
+        <v>1.714339810147985</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04186587868856738</v>
+        <v>0.04093552582882143</v>
       </c>
       <c r="W46">
-        <v>0.2259280258052358</v>
+        <v>0.2261474030095639</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4186587868856737</v>
+        <v>0.4093552582882143</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1739979842586341</v>
+        <v>0.1758979842586341</v>
       </c>
       <c r="C47">
-        <v>-61.48805770757423</v>
+        <v>-77.02262775510206</v>
       </c>
       <c r="D47">
-        <v>370.2442187314588</v>
+        <v>364.8370326047984</v>
       </c>
       <c r="E47">
-        <v>264.5938843522931</v>
+        <v>274.7212682731605</v>
       </c>
       <c r="F47">
-        <v>455.732276439033</v>
+        <v>465.8596603599004</v>
       </c>
       <c r="G47">
         <v>24</v>
@@ -5141,37 +5141,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M47">
-        <v>107.461670784324</v>
+        <v>109.8497079128645</v>
       </c>
       <c r="N47">
-        <v>-63.47167078432399</v>
+        <v>-65.85970791286454</v>
       </c>
       <c r="O47">
-        <v>-6.347167078432399</v>
+        <v>-6.585970791286454</v>
       </c>
       <c r="P47">
-        <v>-57.12450370589159</v>
+        <v>-59.27373712157808</v>
       </c>
       <c r="Q47">
-        <v>-28.32450370589159</v>
+        <v>-30.47373712157808</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1313302780078734</v>
+        <v>0.1329141720450562</v>
       </c>
       <c r="T47">
-        <v>1.714339810147985</v>
+        <v>1.746086843669245</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.04093552582882143</v>
+        <v>0.04004562309341227</v>
       </c>
       <c r="W47">
-        <v>0.2261474030095639</v>
+        <v>0.2263572420745734</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4093552582882143</v>
+        <v>0.4004562309341226</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1758979842586341</v>
+        <v>0.1777979842586341</v>
       </c>
       <c r="C48">
-        <v>-77.02262775510206</v>
+        <v>-92.40153400672637</v>
       </c>
       <c r="D48">
-        <v>364.8370326047984</v>
+        <v>359.5855102740414</v>
       </c>
       <c r="E48">
-        <v>274.7212682731605</v>
+        <v>284.8486521940279</v>
       </c>
       <c r="F48">
-        <v>465.8596603599004</v>
+        <v>475.9870442807678</v>
       </c>
       <c r="G48">
         <v>24</v>
@@ -5223,37 +5223,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M48">
-        <v>109.8497079128645</v>
+        <v>112.237745041405</v>
       </c>
       <c r="N48">
-        <v>-65.85970791286454</v>
+        <v>-68.24774504140505</v>
       </c>
       <c r="O48">
-        <v>-6.585970791286454</v>
+        <v>-6.824774504140506</v>
       </c>
       <c r="P48">
-        <v>-59.27373712157808</v>
+        <v>-61.42297053726455</v>
       </c>
       <c r="Q48">
-        <v>-30.47373712157808</v>
+        <v>-32.62297053726455</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1329141720450562</v>
+        <v>0.1345578356685478</v>
       </c>
       <c r="T48">
-        <v>1.746086843669245</v>
+        <v>1.779031878455457</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.04004562309341227</v>
+        <v>0.03919358855950988</v>
       </c>
       <c r="W48">
-        <v>0.2263572420745734</v>
+        <v>0.2265581518176676</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4004562309341226</v>
+        <v>0.3919358855950987</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1777979842586341</v>
+        <v>0.1796979842586341</v>
       </c>
       <c r="C49">
-        <v>-92.40153400672637</v>
+        <v>-107.6314030270036</v>
       </c>
       <c r="D49">
-        <v>359.5855102740414</v>
+        <v>354.4830251746316</v>
       </c>
       <c r="E49">
-        <v>284.8486521940279</v>
+        <v>294.9760361148954</v>
       </c>
       <c r="F49">
-        <v>475.9870442807678</v>
+        <v>486.1144282016352</v>
       </c>
       <c r="G49">
         <v>24</v>
@@ -5305,37 +5305,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M49">
-        <v>112.237745041405</v>
+        <v>114.6257821699456</v>
       </c>
       <c r="N49">
-        <v>-68.24774504140505</v>
+        <v>-70.6357821699456</v>
       </c>
       <c r="O49">
-        <v>-6.824774504140506</v>
+        <v>-7.063578216994561</v>
       </c>
       <c r="P49">
-        <v>-61.42297053726455</v>
+        <v>-63.57220395295104</v>
       </c>
       <c r="Q49">
-        <v>-32.62297053726455</v>
+        <v>-34.77220395295105</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1345578356685478</v>
+        <v>0.1362647171237122</v>
       </c>
       <c r="T49">
-        <v>1.779031878455457</v>
+        <v>1.813244029964216</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03919358855950988</v>
+        <v>0.03837705546452008</v>
       </c>
       <c r="W49">
-        <v>0.2265581518176676</v>
+        <v>0.2267506903214662</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3919358855950987</v>
+        <v>0.3837705546452008</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1796979842586341</v>
+        <v>0.1815979842586341</v>
       </c>
       <c r="C50">
-        <v>-107.6314030270034</v>
+        <v>-122.7184905215929</v>
       </c>
       <c r="D50">
-        <v>354.4830251746317</v>
+        <v>349.5233216009097</v>
       </c>
       <c r="E50">
-        <v>294.9760361148952</v>
+        <v>305.1034200357626</v>
       </c>
       <c r="F50">
-        <v>486.1144282016352</v>
+        <v>496.2418121225026</v>
       </c>
       <c r="G50">
         <v>24</v>
@@ -5387,37 +5387,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M50">
-        <v>114.6257821699456</v>
+        <v>117.0138192984861</v>
       </c>
       <c r="N50">
-        <v>-70.63578216994559</v>
+        <v>-73.02381929848612</v>
       </c>
       <c r="O50">
-        <v>-7.063578216994559</v>
+        <v>-7.302381929848612</v>
       </c>
       <c r="P50">
-        <v>-63.57220395295103</v>
+        <v>-65.72143736863751</v>
       </c>
       <c r="Q50">
-        <v>-34.77220395295103</v>
+        <v>-36.92143736863751</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1362647171237122</v>
+        <v>0.1380385351065301</v>
       </c>
       <c r="T50">
-        <v>1.813244029964216</v>
+        <v>1.848797834473318</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03837705546452009</v>
+        <v>0.03759385025095846</v>
       </c>
       <c r="W50">
-        <v>0.2267506903214662</v>
+        <v>0.226935370110824</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3837705546452009</v>
+        <v>0.3759385025095846</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1815979842586341</v>
+        <v>0.1834979842586341</v>
       </c>
       <c r="C51">
-        <v>-122.7184905215929</v>
+        <v>-137.6687069233946</v>
       </c>
       <c r="D51">
-        <v>349.5233216009097</v>
+        <v>344.7004891199754</v>
       </c>
       <c r="E51">
-        <v>305.1034200357626</v>
+        <v>315.2308039566301</v>
       </c>
       <c r="F51">
-        <v>496.2418121225026</v>
+        <v>506.36919604337</v>
       </c>
       <c r="G51">
         <v>24</v>
@@ -5469,37 +5469,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M51">
-        <v>117.0138192984861</v>
+        <v>119.4018564270266</v>
       </c>
       <c r="N51">
-        <v>-73.02381929848612</v>
+        <v>-75.41185642702665</v>
       </c>
       <c r="O51">
-        <v>-7.302381929848612</v>
+        <v>-7.541185642702665</v>
       </c>
       <c r="P51">
-        <v>-65.72143736863751</v>
+        <v>-67.87067078432398</v>
       </c>
       <c r="Q51">
-        <v>-36.92143736863751</v>
+        <v>-39.07067078432398</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1380385351065301</v>
+        <v>0.1398833058086607</v>
       </c>
       <c r="T51">
-        <v>1.848797834473318</v>
+        <v>1.885773791162784</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03759385025095846</v>
+        <v>0.03684197324593929</v>
       </c>
       <c r="W51">
-        <v>0.226935370110824</v>
+        <v>0.2271126627086075</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3759385025095846</v>
+        <v>0.3684197324593929</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1834979842586341</v>
+        <v>0.1853979842586341</v>
       </c>
       <c r="C52">
-        <v>-137.6687069233946</v>
+        <v>-152.4876408892439</v>
       </c>
       <c r="D52">
-        <v>344.7004891199754</v>
+        <v>340.0089390749935</v>
       </c>
       <c r="E52">
-        <v>315.2308039566301</v>
+        <v>325.3581878774975</v>
       </c>
       <c r="F52">
-        <v>506.36919604337</v>
+        <v>516.4965799642374</v>
       </c>
       <c r="G52">
         <v>24</v>
@@ -5551,37 +5551,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M52">
-        <v>119.4018564270266</v>
+        <v>121.7898935555672</v>
       </c>
       <c r="N52">
-        <v>-75.41185642702665</v>
+        <v>-77.79989355556719</v>
       </c>
       <c r="O52">
-        <v>-7.541185642702665</v>
+        <v>-7.77998935555672</v>
       </c>
       <c r="P52">
-        <v>-67.87067078432398</v>
+        <v>-70.01990420001047</v>
       </c>
       <c r="Q52">
-        <v>-39.07067078432398</v>
+        <v>-41.21990420001048</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1398833058086607</v>
+        <v>0.1418033732741436</v>
       </c>
       <c r="T52">
-        <v>1.885773791162784</v>
+        <v>1.92425897057427</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.03684197324593929</v>
+        <v>0.03611958161366596</v>
       </c>
       <c r="W52">
-        <v>0.2271126627086075</v>
+        <v>0.2272830026554976</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3684197324593929</v>
+        <v>0.3611958161366596</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1853979842586341</v>
+        <v>0.1872979842586341</v>
       </c>
       <c r="C53">
-        <v>-152.4876408892439</v>
+        <v>-167.1805809035583</v>
       </c>
       <c r="D53">
-        <v>340.0089390749935</v>
+        <v>335.4433829815465</v>
       </c>
       <c r="E53">
-        <v>325.3581878774975</v>
+        <v>335.4855717983648</v>
       </c>
       <c r="F53">
-        <v>516.4965799642374</v>
+        <v>526.6239638851048</v>
       </c>
       <c r="G53">
         <v>24</v>
@@ -5633,37 +5633,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M53">
-        <v>121.7898935555672</v>
+        <v>124.1779306841077</v>
       </c>
       <c r="N53">
-        <v>-77.79989355556719</v>
+        <v>-80.18793068410771</v>
       </c>
       <c r="O53">
-        <v>-7.77998935555672</v>
+        <v>-8.018793068410771</v>
       </c>
       <c r="P53">
-        <v>-70.01990420001047</v>
+        <v>-72.16913761569694</v>
       </c>
       <c r="Q53">
-        <v>-41.21990420001048</v>
+        <v>-43.36913761569694</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1418033732741436</v>
+        <v>0.1438034435506882</v>
       </c>
       <c r="T53">
-        <v>1.92425897057427</v>
+        <v>1.9643476991279</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03611958161366596</v>
+        <v>0.03542497427494162</v>
       </c>
       <c r="W53">
-        <v>0.2272830026554976</v>
+        <v>0.2274467910659688</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3611958161366596</v>
+        <v>0.3542497427494162</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1872979842586341</v>
+        <v>0.1891979842586342</v>
       </c>
       <c r="C54">
-        <v>-167.1805809035583</v>
+        <v>-181.752535164518</v>
       </c>
       <c r="D54">
-        <v>335.4433829815465</v>
+        <v>330.9988126414542</v>
       </c>
       <c r="E54">
-        <v>335.4855717983648</v>
+        <v>345.6129557192322</v>
       </c>
       <c r="F54">
-        <v>526.6239638851048</v>
+        <v>536.7513478059722</v>
       </c>
       <c r="G54">
         <v>24</v>
@@ -5715,37 +5715,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M54">
-        <v>124.1779306841077</v>
+        <v>126.5659678126482</v>
       </c>
       <c r="N54">
-        <v>-80.18793068410771</v>
+        <v>-82.57596781264824</v>
       </c>
       <c r="O54">
-        <v>-8.018793068410771</v>
+        <v>-8.257596781264825</v>
       </c>
       <c r="P54">
-        <v>-72.16913761569694</v>
+        <v>-74.31837103138342</v>
       </c>
       <c r="Q54">
-        <v>-43.36913761569694</v>
+        <v>-45.51837103138342</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1438034435506882</v>
+        <v>0.1458886232007029</v>
       </c>
       <c r="T54">
-        <v>1.9643476991279</v>
+        <v>2.006142331024239</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03542497427494162</v>
+        <v>0.03475657853390499</v>
       </c>
       <c r="W54">
-        <v>0.2274467910659688</v>
+        <v>0.2276043987817052</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3542497427494162</v>
+        <v>0.3475657853390499</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1891979842586342</v>
+        <v>0.1910979842586341</v>
       </c>
       <c r="C55">
-        <v>-181.752535164518</v>
+        <v>-196.2082499099845</v>
       </c>
       <c r="D55">
-        <v>330.9988126414542</v>
+        <v>326.6704818168552</v>
       </c>
       <c r="E55">
-        <v>345.6129557192322</v>
+        <v>355.7403396400997</v>
       </c>
       <c r="F55">
-        <v>536.7513478059722</v>
+        <v>546.8787317268396</v>
       </c>
       <c r="G55">
         <v>24</v>
@@ -5797,37 +5797,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M55">
-        <v>126.5659678126482</v>
+        <v>128.9540049411888</v>
       </c>
       <c r="N55">
-        <v>-82.57596781264824</v>
+        <v>-84.9640049411888</v>
       </c>
       <c r="O55">
-        <v>-8.257596781264825</v>
+        <v>-8.49640049411888</v>
       </c>
       <c r="P55">
-        <v>-74.31837103138342</v>
+        <v>-76.46760444706993</v>
       </c>
       <c r="Q55">
-        <v>-45.51837103138342</v>
+        <v>-47.66760444706993</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1458886232007029</v>
+        <v>0.1480644628355008</v>
       </c>
       <c r="T55">
-        <v>2.006142331024239</v>
+        <v>2.049754120829113</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03475657853390499</v>
+        <v>0.03411293819068452</v>
       </c>
       <c r="W55">
-        <v>0.2276043987817052</v>
+        <v>0.2277561691746366</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3475657853390499</v>
+        <v>0.3411293819068452</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1910979842586341</v>
+        <v>0.1929979842586341</v>
       </c>
       <c r="C56">
-        <v>-196.2082499099845</v>
+        <v>-210.5522263241396</v>
       </c>
       <c r="D56">
-        <v>326.6704818168552</v>
+        <v>322.4538893235675</v>
       </c>
       <c r="E56">
-        <v>355.7403396400997</v>
+        <v>365.8677235609671</v>
       </c>
       <c r="F56">
-        <v>546.8787317268396</v>
+        <v>557.006115647707</v>
       </c>
       <c r="G56">
         <v>24</v>
@@ -5879,37 +5879,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M56">
-        <v>128.9540049411888</v>
+        <v>131.3420420697293</v>
       </c>
       <c r="N56">
-        <v>-84.9640049411888</v>
+        <v>-87.35204206972934</v>
       </c>
       <c r="O56">
-        <v>-8.49640049411888</v>
+        <v>-8.735204206972934</v>
       </c>
       <c r="P56">
-        <v>-76.46760444706993</v>
+        <v>-78.6168378627564</v>
       </c>
       <c r="Q56">
-        <v>-47.66760444706993</v>
+        <v>-49.8168378627564</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1480644628355008</v>
+        <v>0.1503370064540675</v>
       </c>
       <c r="T56">
-        <v>2.049754120829113</v>
+        <v>2.095304212403093</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03411293819068452</v>
+        <v>0.03349270295085389</v>
       </c>
       <c r="W56">
-        <v>0.2277561691746366</v>
+        <v>0.2279024206441886</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3411293819068452</v>
+        <v>0.3349270295085389</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1929979842586341</v>
+        <v>0.1948979842586341</v>
       </c>
       <c r="C57">
-        <v>-210.5522263241396</v>
+        <v>-224.7887361514445</v>
       </c>
       <c r="D57">
-        <v>322.4538893235675</v>
+        <v>318.3447634171299</v>
       </c>
       <c r="E57">
-        <v>365.8677235609671</v>
+        <v>375.9951074818345</v>
       </c>
       <c r="F57">
-        <v>557.006115647707</v>
+        <v>567.1334995685744</v>
       </c>
       <c r="G57">
         <v>24</v>
@@ -5961,37 +5961,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M57">
-        <v>131.3420420697293</v>
+        <v>133.7300791982698</v>
       </c>
       <c r="N57">
-        <v>-87.35204206972934</v>
+        <v>-89.74007919826984</v>
       </c>
       <c r="O57">
-        <v>-8.735204206972934</v>
+        <v>-8.974007919826985</v>
       </c>
       <c r="P57">
-        <v>-78.6168378627564</v>
+        <v>-80.76607127844285</v>
       </c>
       <c r="Q57">
-        <v>-49.8168378627564</v>
+        <v>-51.96607127844285</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1503370064540675</v>
+        <v>0.1527128475098418</v>
       </c>
       <c r="T57">
-        <v>2.095304212403093</v>
+        <v>2.142924762684983</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03349270295085389</v>
+        <v>0.03289461896958865</v>
       </c>
       <c r="W57">
-        <v>0.2279024206441886</v>
+        <v>0.228043448846971</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3349270295085389</v>
+        <v>0.3289461896958865</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1948979842586341</v>
+        <v>0.1967979842586341</v>
       </c>
       <c r="C58">
-        <v>-224.7887361514445</v>
+        <v>-238.9218361317829</v>
       </c>
       <c r="D58">
-        <v>318.3447634171299</v>
+        <v>314.339047357659</v>
       </c>
       <c r="E58">
-        <v>375.9951074818345</v>
+        <v>386.1224914027019</v>
       </c>
       <c r="F58">
-        <v>567.1334995685744</v>
+        <v>577.2608834894419</v>
       </c>
       <c r="G58">
         <v>24</v>
@@ -6043,37 +6043,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M58">
-        <v>133.7300791982698</v>
+        <v>136.1181163268104</v>
       </c>
       <c r="N58">
-        <v>-89.74007919826984</v>
+        <v>-92.1281163268104</v>
       </c>
       <c r="O58">
-        <v>-8.974007919826985</v>
+        <v>-9.21281163268104</v>
       </c>
       <c r="P58">
-        <v>-80.76607127844285</v>
+        <v>-82.91530469412936</v>
       </c>
       <c r="Q58">
-        <v>-51.96607127844285</v>
+        <v>-54.11530469412936</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1527128475098418</v>
+        <v>0.1551991928007683</v>
       </c>
       <c r="T58">
-        <v>2.142924762684983</v>
+        <v>2.192760222282307</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03289461896958865</v>
+        <v>0.03231752039117481</v>
       </c>
       <c r="W58">
-        <v>0.228043448846971</v>
+        <v>0.228179528691761</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3289461896958865</v>
+        <v>0.323175203911748</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1967979842586341</v>
+        <v>0.1986979842586342</v>
       </c>
       <c r="C59">
-        <v>-238.9218361317829</v>
+        <v>-252.9553813593245</v>
       </c>
       <c r="D59">
-        <v>314.339047357659</v>
+        <v>310.4328860509848</v>
       </c>
       <c r="E59">
-        <v>386.1224914027019</v>
+        <v>396.2498753235693</v>
       </c>
       <c r="F59">
-        <v>577.2608834894419</v>
+        <v>587.3882674103093</v>
       </c>
       <c r="G59">
         <v>24</v>
@@ -6125,37 +6125,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M59">
-        <v>136.1181163268104</v>
+        <v>138.5061534553509</v>
       </c>
       <c r="N59">
-        <v>-92.1281163268104</v>
+        <v>-94.51615345535093</v>
       </c>
       <c r="O59">
-        <v>-9.21281163268104</v>
+        <v>-9.451615345535094</v>
       </c>
       <c r="P59">
-        <v>-82.91530469412936</v>
+        <v>-85.06453810981584</v>
       </c>
       <c r="Q59">
-        <v>-54.11530469412936</v>
+        <v>-56.26453810981585</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1551991928007683</v>
+        <v>0.1578039354865009</v>
       </c>
       <c r="T59">
-        <v>2.192760222282307</v>
+        <v>2.244968799003315</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03231752039117481</v>
+        <v>0.03176032176374077</v>
       </c>
       <c r="W59">
-        <v>0.228179528691761</v>
+        <v>0.2283109161281099</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.323175203911748</v>
+        <v>0.3176032176374076</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1986979842586341</v>
+        <v>0.2005979842586341</v>
       </c>
       <c r="C60">
-        <v>-252.9553813593243</v>
+        <v>-266.8930376575852</v>
       </c>
       <c r="D60">
-        <v>310.4328860509848</v>
+        <v>306.6226136735913</v>
       </c>
       <c r="E60">
-        <v>396.2498753235692</v>
+        <v>406.3772592444366</v>
       </c>
       <c r="F60">
-        <v>587.3882674103091</v>
+        <v>597.5156513311765</v>
       </c>
       <c r="G60">
         <v>24</v>
@@ -6207,37 +6207,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M60">
-        <v>138.5061534553509</v>
+        <v>140.8941905838914</v>
       </c>
       <c r="N60">
-        <v>-94.5161534553509</v>
+        <v>-96.90419058389143</v>
       </c>
       <c r="O60">
-        <v>-9.451615345535091</v>
+        <v>-9.690419058389145</v>
       </c>
       <c r="P60">
-        <v>-85.06453810981581</v>
+        <v>-87.2137715255023</v>
       </c>
       <c r="Q60">
-        <v>-56.26453810981582</v>
+        <v>-58.4137715255023</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1578039354865008</v>
+        <v>0.1605357387910497</v>
       </c>
       <c r="T60">
-        <v>2.244968799003314</v>
+        <v>2.299724135564371</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03176032176374077</v>
+        <v>0.03122201122537228</v>
       </c>
       <c r="W60">
-        <v>0.2283109161281099</v>
+        <v>0.2284378497530572</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3176032176374076</v>
+        <v>0.3122201122537228</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2005979842586341</v>
+        <v>0.2024979842586341</v>
       </c>
       <c r="C61">
-        <v>-266.8930376575852</v>
+        <v>-280.7382930541844</v>
       </c>
       <c r="D61">
-        <v>306.6226136735913</v>
+        <v>302.9047421978596</v>
       </c>
       <c r="E61">
-        <v>406.3772592444366</v>
+        <v>416.5046431653041</v>
       </c>
       <c r="F61">
-        <v>597.5156513311765</v>
+        <v>607.643035252044</v>
       </c>
       <c r="G61">
         <v>24</v>
@@ -6289,37 +6289,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M61">
-        <v>140.8941905838914</v>
+        <v>143.282227712432</v>
       </c>
       <c r="N61">
-        <v>-96.90419058389143</v>
+        <v>-99.29222771243199</v>
       </c>
       <c r="O61">
-        <v>-9.690419058389145</v>
+        <v>-9.9292227712432</v>
       </c>
       <c r="P61">
-        <v>-87.2137715255023</v>
+        <v>-89.36300494118879</v>
       </c>
       <c r="Q61">
-        <v>-58.4137715255023</v>
+        <v>-60.56300494118879</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1605357387910497</v>
+        <v>0.1634041322608259</v>
       </c>
       <c r="T61">
-        <v>2.299724135564371</v>
+        <v>2.35721723895348</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03122201122537228</v>
+        <v>0.03070164437161607</v>
       </c>
       <c r="W61">
-        <v>0.2284378497530572</v>
+        <v>0.2285605522571729</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3122201122537228</v>
+        <v>0.3070164437161607</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2024979842586341</v>
+        <v>0.2043979842586341</v>
       </c>
       <c r="C62">
-        <v>-280.7382930541844</v>
+        <v>-294.4944684307956</v>
       </c>
       <c r="D62">
-        <v>302.9047421978596</v>
+        <v>299.2759507421158</v>
       </c>
       <c r="E62">
-        <v>416.5046431653041</v>
+        <v>426.6320270861714</v>
       </c>
       <c r="F62">
-        <v>607.643035252044</v>
+        <v>617.7704191729114</v>
       </c>
       <c r="G62">
         <v>24</v>
@@ -6371,37 +6371,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M62">
-        <v>143.282227712432</v>
+        <v>145.6702648409725</v>
       </c>
       <c r="N62">
-        <v>-99.29222771243199</v>
+        <v>-101.6802648409725</v>
       </c>
       <c r="O62">
-        <v>-9.9292227712432</v>
+        <v>-10.16802648409725</v>
       </c>
       <c r="P62">
-        <v>-89.36300494118879</v>
+        <v>-91.51223835687527</v>
       </c>
       <c r="Q62">
-        <v>-60.56300494118879</v>
+        <v>-62.71223835687528</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1634041322608259</v>
+        <v>0.1664196228316163</v>
       </c>
       <c r="T62">
-        <v>2.35721723895348</v>
+        <v>2.417658706618954</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03070164437161607</v>
+        <v>0.03019833872617974</v>
       </c>
       <c r="W62">
-        <v>0.2285605522571729</v>
+        <v>0.2286792317283668</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3070164437161607</v>
+        <v>0.3019833872617974</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2043979842586341</v>
+        <v>0.2062979842586341</v>
       </c>
       <c r="C63">
-        <v>-294.4944684307956</v>
+        <v>-308.1647274166464</v>
       </c>
       <c r="D63">
-        <v>299.2759507421158</v>
+        <v>295.7330756771324</v>
       </c>
       <c r="E63">
-        <v>426.6320270861714</v>
+        <v>436.7594110070388</v>
       </c>
       <c r="F63">
-        <v>617.7704191729114</v>
+        <v>627.8978030937787</v>
       </c>
       <c r="G63">
         <v>24</v>
@@ -6453,37 +6453,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M63">
-        <v>145.6702648409725</v>
+        <v>148.058301969513</v>
       </c>
       <c r="N63">
-        <v>-101.6802648409725</v>
+        <v>-104.068301969513</v>
       </c>
       <c r="O63">
-        <v>-10.16802648409725</v>
+        <v>-10.4068301969513</v>
       </c>
       <c r="P63">
-        <v>-91.51223835687527</v>
+        <v>-93.66147177256173</v>
       </c>
       <c r="Q63">
-        <v>-62.71223835687528</v>
+        <v>-64.86147177256173</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1664196228316163</v>
+        <v>0.1695938234324483</v>
       </c>
       <c r="T63">
-        <v>2.417658706618954</v>
+        <v>2.481281304161558</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03019833872617974</v>
+        <v>0.02971126874672524</v>
       </c>
       <c r="W63">
-        <v>0.2286792317283668</v>
+        <v>0.2287940828295222</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3019833872617974</v>
+        <v>0.2971126874672524</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2062979842586341</v>
+        <v>0.2081979842586341</v>
       </c>
       <c r="C64">
-        <v>-308.1647274166464</v>
+        <v>-321.7520855875125</v>
       </c>
       <c r="D64">
-        <v>295.7330756771324</v>
+        <v>292.2731014271337</v>
       </c>
       <c r="E64">
-        <v>436.7594110070388</v>
+        <v>446.8867949279063</v>
       </c>
       <c r="F64">
-        <v>627.8978030937787</v>
+        <v>638.0251870146462</v>
       </c>
       <c r="G64">
         <v>24</v>
@@ -6535,37 +6535,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M64">
-        <v>148.058301969513</v>
+        <v>150.4463390980536</v>
       </c>
       <c r="N64">
-        <v>-104.068301969513</v>
+        <v>-106.4563390980536</v>
       </c>
       <c r="O64">
-        <v>-10.4068301969513</v>
+        <v>-10.64563390980536</v>
       </c>
       <c r="P64">
-        <v>-93.66147177256173</v>
+        <v>-95.81070518824824</v>
       </c>
       <c r="Q64">
-        <v>-64.86147177256173</v>
+        <v>-67.01070518824824</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1695938234324483</v>
+        <v>0.1729396024441361</v>
       </c>
       <c r="T64">
-        <v>2.481281304161558</v>
+        <v>2.548342961030789</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02971126874672524</v>
+        <v>0.02923966130630102</v>
       </c>
       <c r="W64">
-        <v>0.2287940828295222</v>
+        <v>0.2289052878639742</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2971126874672524</v>
+        <v>0.2923966130630102</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2081979842586341</v>
+        <v>0.2100979842586341</v>
       </c>
       <c r="C65">
-        <v>-321.7520855875125</v>
+        <v>-335.2594190264299</v>
       </c>
       <c r="D65">
-        <v>292.2731014271337</v>
+        <v>288.8931519090837</v>
       </c>
       <c r="E65">
-        <v>446.8867949279063</v>
+        <v>457.0141788487737</v>
       </c>
       <c r="F65">
-        <v>638.0251870146462</v>
+        <v>648.1525709355136</v>
       </c>
       <c r="G65">
         <v>24</v>
@@ -6617,37 +6617,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M65">
-        <v>150.4463390980536</v>
+        <v>152.8343762265941</v>
       </c>
       <c r="N65">
-        <v>-106.4563390980536</v>
+        <v>-108.8443762265941</v>
       </c>
       <c r="O65">
-        <v>-10.64563390980536</v>
+        <v>-10.88443762265941</v>
       </c>
       <c r="P65">
-        <v>-95.81070518824824</v>
+        <v>-97.95993860393472</v>
       </c>
       <c r="Q65">
-        <v>-67.01070518824824</v>
+        <v>-69.15993860393472</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1729396024441361</v>
+        <v>0.1764712580675843</v>
       </c>
       <c r="T65">
-        <v>2.548342961030789</v>
+        <v>2.619130265503867</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02923966130630102</v>
+        <v>0.02878279159839007</v>
       </c>
       <c r="W65">
-        <v>0.2289052878639742</v>
+        <v>0.2290130177410996</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2923966130630102</v>
+        <v>0.2878279159839007</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2100979842586341</v>
+        <v>0.2119979842586341</v>
       </c>
       <c r="C66">
-        <v>-335.2594190264299</v>
+        <v>-348.689472297204</v>
       </c>
       <c r="D66">
-        <v>288.8931519090837</v>
+        <v>285.590482559177</v>
       </c>
       <c r="E66">
-        <v>457.0141788487737</v>
+        <v>467.141562769641</v>
       </c>
       <c r="F66">
-        <v>648.1525709355136</v>
+        <v>658.279954856381</v>
       </c>
       <c r="G66">
         <v>24</v>
@@ -6699,37 +6699,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M66">
-        <v>152.8343762265941</v>
+        <v>155.2224133551346</v>
       </c>
       <c r="N66">
-        <v>-108.8443762265941</v>
+        <v>-111.2324133551347</v>
       </c>
       <c r="O66">
-        <v>-10.88443762265941</v>
+        <v>-11.12324133551347</v>
       </c>
       <c r="P66">
-        <v>-97.95993860393472</v>
+        <v>-100.1091720196212</v>
       </c>
       <c r="Q66">
-        <v>-69.15993860393472</v>
+        <v>-71.30917201962119</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1764712580675843</v>
+        <v>0.180204722583801</v>
       </c>
       <c r="T66">
-        <v>2.619130265503867</v>
+        <v>2.693962558803978</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02878279159839007</v>
+        <v>0.0283399794199533</v>
       </c>
       <c r="W66">
-        <v>0.2290130177410996</v>
+        <v>0.229117432852775</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2878279159839007</v>
+        <v>0.283399794199533</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2119979842586341</v>
+        <v>0.2138979842586341</v>
       </c>
       <c r="C67">
-        <v>-348.689472297204</v>
+        <v>-362.0448658771731</v>
       </c>
       <c r="D67">
-        <v>285.590482559177</v>
+        <v>282.3624729000753</v>
       </c>
       <c r="E67">
-        <v>467.141562769641</v>
+        <v>477.2689466905084</v>
       </c>
       <c r="F67">
-        <v>658.279954856381</v>
+        <v>668.4073387772484</v>
       </c>
       <c r="G67">
         <v>24</v>
@@ -6781,37 +6781,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M67">
-        <v>155.2224133551346</v>
+        <v>157.6104504836752</v>
       </c>
       <c r="N67">
-        <v>-111.2324133551347</v>
+        <v>-113.6204504836752</v>
       </c>
       <c r="O67">
-        <v>-11.12324133551347</v>
+        <v>-11.36204504836752</v>
       </c>
       <c r="P67">
-        <v>-100.1091720196212</v>
+        <v>-102.2584054353077</v>
       </c>
       <c r="Q67">
-        <v>-71.30917201962119</v>
+        <v>-73.45840543530767</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.180204722583801</v>
+        <v>0.1841578026597952</v>
       </c>
       <c r="T67">
-        <v>2.693962558803978</v>
+        <v>2.773196751709976</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0283399794199533</v>
+        <v>0.02791058579237825</v>
       </c>
       <c r="W67">
-        <v>0.229117432852775</v>
+        <v>0.2292186838701572</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.283399794199533</v>
+        <v>0.2791058579237825</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2138979842586341</v>
+        <v>0.2157979842586341</v>
       </c>
       <c r="C68">
-        <v>-362.0448658771731</v>
+        <v>-375.3281030915358</v>
       </c>
       <c r="D68">
-        <v>282.3624729000753</v>
+        <v>279.20661960658</v>
       </c>
       <c r="E68">
-        <v>477.2689466905084</v>
+        <v>487.3963306113759</v>
       </c>
       <c r="F68">
-        <v>668.4073387772484</v>
+        <v>678.5347226981158</v>
       </c>
       <c r="G68">
         <v>24</v>
@@ -6863,37 +6863,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M68">
-        <v>157.6104504836752</v>
+        <v>159.9984876122157</v>
       </c>
       <c r="N68">
-        <v>-113.6204504836752</v>
+        <v>-116.0084876122157</v>
       </c>
       <c r="O68">
-        <v>-11.36204504836752</v>
+        <v>-11.60084876122157</v>
       </c>
       <c r="P68">
-        <v>-102.2584054353077</v>
+        <v>-104.4076388509941</v>
       </c>
       <c r="Q68">
-        <v>-73.45840543530767</v>
+        <v>-75.60763885099415</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1841578026597952</v>
+        <v>0.1883504633464557</v>
       </c>
       <c r="T68">
-        <v>2.773196751709976</v>
+        <v>2.85723301691331</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02791058579237825</v>
+        <v>0.02749400988502932</v>
       </c>
       <c r="W68">
-        <v>0.2292186838701572</v>
+        <v>0.2293169124691101</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2791058579237825</v>
+        <v>0.2749400988502931</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2157979842586341</v>
+        <v>0.2176979842586341</v>
       </c>
       <c r="C69">
-        <v>-375.3281030915358</v>
+        <v>-388.5415765878012</v>
       </c>
       <c r="D69">
-        <v>279.20661960658</v>
+        <v>276.1205300311821</v>
       </c>
       <c r="E69">
-        <v>487.3963306113759</v>
+        <v>497.5237145322433</v>
       </c>
       <c r="F69">
-        <v>678.5347226981158</v>
+        <v>688.6621066189832</v>
       </c>
       <c r="G69">
         <v>24</v>
@@ -6945,37 +6945,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M69">
-        <v>159.9984876122157</v>
+        <v>162.3865247407562</v>
       </c>
       <c r="N69">
-        <v>-116.0084876122157</v>
+        <v>-118.3965247407562</v>
       </c>
       <c r="O69">
-        <v>-11.60084876122157</v>
+        <v>-11.83965247407563</v>
       </c>
       <c r="P69">
-        <v>-104.4076388509941</v>
+        <v>-106.5568722666806</v>
       </c>
       <c r="Q69">
-        <v>-75.60763885099415</v>
+        <v>-77.75687226668063</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1883504633464557</v>
+        <v>0.1928051653260324</v>
       </c>
       <c r="T69">
-        <v>2.85723301691331</v>
+        <v>2.946521548691851</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02749400988502932</v>
+        <v>0.02708968621024948</v>
       </c>
       <c r="W69">
-        <v>0.2293169124691101</v>
+        <v>0.2294122519916232</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2749400988502931</v>
+        <v>0.2708968621024948</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2176979842586341</v>
+        <v>0.2195979842586342</v>
       </c>
       <c r="C70">
-        <v>-388.5415765878012</v>
+        <v>-401.6875743855621</v>
       </c>
       <c r="D70">
-        <v>276.1205300311821</v>
+        <v>273.1019161542885</v>
       </c>
       <c r="E70">
-        <v>497.5237145322433</v>
+        <v>507.6510984531106</v>
       </c>
       <c r="F70">
-        <v>688.6621066189832</v>
+        <v>698.7894905398506</v>
       </c>
       <c r="G70">
         <v>24</v>
@@ -7027,37 +7027,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M70">
-        <v>162.3865247407562</v>
+        <v>164.7745618692968</v>
       </c>
       <c r="N70">
-        <v>-118.3965247407562</v>
+        <v>-120.7845618692968</v>
       </c>
       <c r="O70">
-        <v>-11.83965247407563</v>
+        <v>-12.07845618692968</v>
       </c>
       <c r="P70">
-        <v>-106.5568722666806</v>
+        <v>-108.7061056823671</v>
       </c>
       <c r="Q70">
-        <v>-77.75687226668063</v>
+        <v>-79.90610568236711</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1928051653260324</v>
+        <v>0.1975472674333238</v>
       </c>
       <c r="T70">
-        <v>2.946521548691851</v>
+        <v>3.041570630907717</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02708968621024948</v>
+        <v>0.02669708206227485</v>
       </c>
       <c r="W70">
-        <v>0.2294122519916232</v>
+        <v>0.2295048280497156</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2708968621024948</v>
+        <v>0.2669708206227485</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2195979842586342</v>
+        <v>0.2214979842586342</v>
       </c>
       <c r="C71">
-        <v>-401.6875743855621</v>
+        <v>-414.7682855337319</v>
       </c>
       <c r="D71">
-        <v>273.1019161542885</v>
+        <v>270.1485889269862</v>
       </c>
       <c r="E71">
-        <v>507.6510984531106</v>
+        <v>517.7784823739781</v>
       </c>
       <c r="F71">
-        <v>698.7894905398506</v>
+        <v>708.9168744607181</v>
       </c>
       <c r="G71">
         <v>24</v>
@@ -7109,37 +7109,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M71">
-        <v>164.7745618692968</v>
+        <v>167.1625989978373</v>
       </c>
       <c r="N71">
-        <v>-120.7845618692968</v>
+        <v>-123.1725989978373</v>
       </c>
       <c r="O71">
-        <v>-12.07845618692968</v>
+        <v>-12.31725989978374</v>
       </c>
       <c r="P71">
-        <v>-108.7061056823671</v>
+        <v>-110.8553390980536</v>
       </c>
       <c r="Q71">
-        <v>-79.90610568236711</v>
+        <v>-82.05533909805361</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1975472674333238</v>
+        <v>0.2026055096811012</v>
       </c>
       <c r="T71">
-        <v>3.041570630907717</v>
+        <v>3.142956318604641</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02669708206227485</v>
+        <v>0.02631569517567091</v>
       </c>
       <c r="W71">
-        <v>0.2295048280497156</v>
+        <v>0.2295947590775768</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2669708206227485</v>
+        <v>0.2631569517567092</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2214979842586342</v>
+        <v>0.2233979842586341</v>
       </c>
       <c r="C72">
-        <v>-414.7682855337319</v>
+        <v>-427.7858054046436</v>
       </c>
       <c r="D72">
-        <v>270.1485889269862</v>
+        <v>267.2584529769419</v>
       </c>
       <c r="E72">
-        <v>517.7784823739781</v>
+        <v>527.9058662948455</v>
       </c>
       <c r="F72">
-        <v>708.9168744607181</v>
+        <v>719.0442583815855</v>
       </c>
       <c r="G72">
         <v>24</v>
@@ -7191,37 +7191,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M72">
-        <v>167.1625989978373</v>
+        <v>169.5506361263779</v>
       </c>
       <c r="N72">
-        <v>-123.1725989978373</v>
+        <v>-125.5606361263779</v>
       </c>
       <c r="O72">
-        <v>-12.31725989978374</v>
+        <v>-12.55606361263779</v>
       </c>
       <c r="P72">
-        <v>-110.8553390980536</v>
+        <v>-113.0045725137401</v>
       </c>
       <c r="Q72">
-        <v>-82.05533909805361</v>
+        <v>-84.20457251374009</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2026055096811012</v>
+        <v>0.2080125962218289</v>
       </c>
       <c r="T72">
-        <v>3.142956318604641</v>
+        <v>3.251334122694457</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02631569517567091</v>
+        <v>0.02594505158164738</v>
       </c>
       <c r="W72">
-        <v>0.2295947590775768</v>
+        <v>0.2296821568370475</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2631569517567092</v>
+        <v>0.2594505158164738</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2233979842586341</v>
+        <v>0.2252979842586341</v>
       </c>
       <c r="C73">
-        <v>-427.7858054046433</v>
+        <v>-440.7421406519197</v>
       </c>
       <c r="D73">
-        <v>267.258452976942</v>
+        <v>264.429501650533</v>
       </c>
       <c r="E73">
-        <v>527.9058662948454</v>
+        <v>538.0332502157128</v>
       </c>
       <c r="F73">
-        <v>719.0442583815853</v>
+        <v>729.1716423024527</v>
       </c>
       <c r="G73">
         <v>24</v>
@@ -7273,37 +7273,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M73">
-        <v>169.5506361263778</v>
+        <v>171.9386732549183</v>
       </c>
       <c r="N73">
-        <v>-125.5606361263778</v>
+        <v>-127.9486732549183</v>
       </c>
       <c r="O73">
-        <v>-12.55606361263779</v>
+        <v>-12.79486732549184</v>
       </c>
       <c r="P73">
-        <v>-113.0045725137401</v>
+        <v>-115.1538059294265</v>
       </c>
       <c r="Q73">
-        <v>-84.20457251374006</v>
+        <v>-86.35380592942651</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2080125962218288</v>
+        <v>0.2138059032297513</v>
       </c>
       <c r="T73">
-        <v>3.251334122694455</v>
+        <v>3.367453198504971</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02594505158164738</v>
+        <v>0.0255847036430134</v>
       </c>
       <c r="W73">
-        <v>0.2296821568370475</v>
+        <v>0.2297671268809775</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2594505158164738</v>
+        <v>0.255847036430134</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2252979842586341</v>
+        <v>0.2271979842586341</v>
       </c>
       <c r="C74">
-        <v>-440.7421406519197</v>
+        <v>-453.6392138567633</v>
       </c>
       <c r="D74">
-        <v>264.429501650533</v>
+        <v>261.6598123665569</v>
       </c>
       <c r="E74">
-        <v>538.0332502157128</v>
+        <v>548.1606341365803</v>
       </c>
       <c r="F74">
-        <v>729.1716423024527</v>
+        <v>739.2990262233202</v>
       </c>
       <c r="G74">
         <v>24</v>
@@ -7355,37 +7355,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M74">
-        <v>171.9386732549183</v>
+        <v>174.3267103834589</v>
       </c>
       <c r="N74">
-        <v>-127.9486732549183</v>
+        <v>-130.3367103834589</v>
       </c>
       <c r="O74">
-        <v>-12.79486732549184</v>
+        <v>-13.03367103834589</v>
       </c>
       <c r="P74">
-        <v>-115.1538059294265</v>
+        <v>-117.303039345113</v>
       </c>
       <c r="Q74">
-        <v>-86.35380592942651</v>
+        <v>-88.50303934511304</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2138059032297513</v>
+        <v>0.2200283440901124</v>
       </c>
       <c r="T74">
-        <v>3.367453198504971</v>
+        <v>3.492173687338489</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0255847036430134</v>
+        <v>0.02523422825064335</v>
       </c>
       <c r="W74">
-        <v>0.2297671268809775</v>
+        <v>0.2298497689784983</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.255847036430134</v>
+        <v>0.2523422825064334</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2271979842586341</v>
+        <v>0.2290979842586341</v>
       </c>
       <c r="C75">
-        <v>-453.6392138567633</v>
+        <v>-466.4788678852767</v>
       </c>
       <c r="D75">
-        <v>261.6598123665569</v>
+        <v>258.9475422589109</v>
       </c>
       <c r="E75">
-        <v>548.1606341365803</v>
+        <v>558.2880180574476</v>
       </c>
       <c r="F75">
-        <v>739.2990262233202</v>
+        <v>749.4264101441876</v>
       </c>
       <c r="G75">
         <v>24</v>
@@ -7437,37 +7437,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M75">
-        <v>174.3267103834589</v>
+        <v>176.7147475119994</v>
       </c>
       <c r="N75">
-        <v>-130.3367103834589</v>
+        <v>-132.7247475119995</v>
       </c>
       <c r="O75">
-        <v>-13.03367103834589</v>
+        <v>-13.27247475119995</v>
       </c>
       <c r="P75">
-        <v>-117.303039345113</v>
+        <v>-119.4522727607995</v>
       </c>
       <c r="Q75">
-        <v>-88.50303934511304</v>
+        <v>-90.65227276079951</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2200283440901124</v>
+        <v>0.2267294342474244</v>
       </c>
       <c r="T75">
-        <v>3.492173687338489</v>
+        <v>3.626488059928431</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02523422825064335</v>
+        <v>0.02489322516617519</v>
       </c>
       <c r="W75">
-        <v>0.2298497689784983</v>
+        <v>0.2299301775058159</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2523422825064334</v>
+        <v>0.2489322516617518</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2290979842586341</v>
+        <v>0.2309979842586341</v>
       </c>
       <c r="C76">
-        <v>-466.4788678852767</v>
+        <v>-479.2628699775646</v>
       </c>
       <c r="D76">
-        <v>258.9475422589109</v>
+        <v>256.2909240874903</v>
       </c>
       <c r="E76">
-        <v>558.2880180574476</v>
+        <v>568.415401978315</v>
       </c>
       <c r="F76">
-        <v>749.4264101441876</v>
+        <v>759.5537940650549</v>
       </c>
       <c r="G76">
         <v>24</v>
@@ -7519,37 +7519,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M76">
-        <v>176.7147475119994</v>
+        <v>179.10278464054</v>
       </c>
       <c r="N76">
-        <v>-132.7247475119995</v>
+        <v>-135.11278464054</v>
       </c>
       <c r="O76">
-        <v>-13.27247475119995</v>
+        <v>-13.511278464054</v>
       </c>
       <c r="P76">
-        <v>-119.4522727607995</v>
+        <v>-121.601506176486</v>
       </c>
       <c r="Q76">
-        <v>-90.65227276079951</v>
+        <v>-92.80150617648599</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2267294342474244</v>
+        <v>0.2339666116173215</v>
       </c>
       <c r="T76">
-        <v>3.626488059928431</v>
+        <v>3.771547582325569</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02489322516617519</v>
+        <v>0.02456131549729286</v>
       </c>
       <c r="W76">
-        <v>0.2299301775058159</v>
+        <v>0.2300084418057383</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2489322516617518</v>
+        <v>0.2456131549729285</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2309979842586341</v>
+        <v>0.2328979842586341</v>
       </c>
       <c r="C77">
-        <v>-479.2628699775646</v>
+        <v>-491.9929155876841</v>
       </c>
       <c r="D77">
-        <v>256.2909240874903</v>
+        <v>253.6882623982383</v>
       </c>
       <c r="E77">
-        <v>568.415401978315</v>
+        <v>578.5427858991825</v>
       </c>
       <c r="F77">
-        <v>759.5537940650549</v>
+        <v>769.6811779859224</v>
       </c>
       <c r="G77">
         <v>24</v>
@@ -7601,37 +7601,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M77">
-        <v>179.10278464054</v>
+        <v>181.4908217690805</v>
       </c>
       <c r="N77">
-        <v>-135.11278464054</v>
+        <v>-137.5008217690805</v>
       </c>
       <c r="O77">
-        <v>-13.511278464054</v>
+        <v>-13.75008217690805</v>
       </c>
       <c r="P77">
-        <v>-121.601506176486</v>
+        <v>-123.7507395921725</v>
       </c>
       <c r="Q77">
-        <v>-92.80150617648599</v>
+        <v>-94.95073959217247</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2339666116173215</v>
+        <v>0.2418068871013765</v>
       </c>
       <c r="T77">
-        <v>3.771547582325569</v>
+        <v>3.928695398255801</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02456131549729286</v>
+        <v>0.02423814029338111</v>
       </c>
       <c r="W77">
-        <v>0.2300084418057383</v>
+        <v>0.2300846465188207</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2456131549729285</v>
+        <v>0.2423814029338112</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2328979842586341</v>
+        <v>0.2347979842586341</v>
       </c>
       <c r="C78">
-        <v>-491.9929155876841</v>
+        <v>-504.6706319919766</v>
       </c>
       <c r="D78">
-        <v>253.6882623982383</v>
+        <v>251.1379299148132</v>
       </c>
       <c r="E78">
-        <v>578.5427858991825</v>
+        <v>588.6701698200499</v>
       </c>
       <c r="F78">
-        <v>769.6811779859224</v>
+        <v>779.8085619067898</v>
       </c>
       <c r="G78">
         <v>24</v>
@@ -7683,37 +7683,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M78">
-        <v>181.4908217690805</v>
+        <v>183.8788588976211</v>
       </c>
       <c r="N78">
-        <v>-137.5008217690805</v>
+        <v>-139.888858897621</v>
       </c>
       <c r="O78">
-        <v>-13.75008217690805</v>
+        <v>-13.98888588976211</v>
       </c>
       <c r="P78">
-        <v>-123.7507395921725</v>
+        <v>-125.8999730078589</v>
       </c>
       <c r="Q78">
-        <v>-94.95073959217247</v>
+        <v>-97.09997300785895</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2418068871013765</v>
+        <v>0.2503289256710016</v>
       </c>
       <c r="T78">
-        <v>3.928695398255801</v>
+        <v>4.099508241658227</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02423814029338111</v>
+        <v>0.02392335925060993</v>
       </c>
       <c r="W78">
-        <v>0.2300846465188207</v>
+        <v>0.2301588718887062</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2423814029338112</v>
+        <v>0.2392335925060993</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2347979842586341</v>
+        <v>0.2366979842586341</v>
       </c>
       <c r="C79">
-        <v>-504.6706319919766</v>
+        <v>-517.2975816819181</v>
       </c>
       <c r="D79">
-        <v>251.1379299148132</v>
+        <v>248.638364145739</v>
       </c>
       <c r="E79">
-        <v>588.6701698200499</v>
+        <v>598.7975537409172</v>
       </c>
       <c r="F79">
-        <v>779.8085619067898</v>
+        <v>789.9359458276572</v>
       </c>
       <c r="G79">
         <v>24</v>
@@ -7765,37 +7765,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M79">
-        <v>183.8788588976211</v>
+        <v>186.2668960261616</v>
       </c>
       <c r="N79">
-        <v>-139.888858897621</v>
+        <v>-142.2768960261616</v>
       </c>
       <c r="O79">
-        <v>-13.98888588976211</v>
+        <v>-14.22768960261616</v>
       </c>
       <c r="P79">
-        <v>-125.8999730078589</v>
+        <v>-128.0492064235454</v>
       </c>
       <c r="Q79">
-        <v>-97.09997300785895</v>
+        <v>-99.24920642354543</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2503289256710016</v>
+        <v>0.2596256950196835</v>
       </c>
       <c r="T79">
-        <v>4.099508241658227</v>
+        <v>4.285849525369965</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02392335925060993</v>
+        <v>0.02361664951662775</v>
       </c>
       <c r="W79">
-        <v>0.2301588718887062</v>
+        <v>0.2302311940439792</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2392335925060993</v>
+        <v>0.2361664951662774</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2366979842586341</v>
+        <v>0.2385979842586341</v>
       </c>
       <c r="C80">
-        <v>-517.2975816819181</v>
+        <v>-529.8752655563533</v>
       </c>
       <c r="D80">
-        <v>248.638364145739</v>
+        <v>246.1880641921713</v>
       </c>
       <c r="E80">
-        <v>598.7975537409172</v>
+        <v>608.9249376617846</v>
       </c>
       <c r="F80">
-        <v>789.9359458276572</v>
+        <v>800.0633297485246</v>
       </c>
       <c r="G80">
         <v>24</v>
@@ -7847,37 +7847,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M80">
-        <v>186.2668960261616</v>
+        <v>188.6549331547021</v>
       </c>
       <c r="N80">
-        <v>-142.2768960261616</v>
+        <v>-144.6649331547021</v>
       </c>
       <c r="O80">
-        <v>-14.22768960261616</v>
+        <v>-14.46649331547021</v>
       </c>
       <c r="P80">
-        <v>-128.0492064235454</v>
+        <v>-130.1984398392319</v>
       </c>
       <c r="Q80">
-        <v>-99.24920642354543</v>
+        <v>-101.3984398392319</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2596256950196835</v>
+        <v>0.2698078709730018</v>
       </c>
       <c r="T80">
-        <v>4.285849525369965</v>
+        <v>4.48993759800663</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02361664951662775</v>
+        <v>0.02331770458603753</v>
       </c>
       <c r="W80">
-        <v>0.2302311940439792</v>
+        <v>0.2303016852586124</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2361664951662774</v>
+        <v>0.2331770458603751</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2385979842586341</v>
+        <v>0.2404979842586341</v>
       </c>
       <c r="C81">
-        <v>-529.8752655563533</v>
+        <v>-542.4051259268165</v>
       </c>
       <c r="D81">
-        <v>246.1880641921713</v>
+        <v>243.7855877425756</v>
       </c>
       <c r="E81">
-        <v>608.9249376617846</v>
+        <v>619.0523215826521</v>
       </c>
       <c r="F81">
-        <v>800.0633297485246</v>
+        <v>810.190713669392</v>
       </c>
       <c r="G81">
         <v>24</v>
@@ -7929,37 +7929,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M81">
-        <v>188.6549331547021</v>
+        <v>191.0429702832427</v>
       </c>
       <c r="N81">
-        <v>-144.6649331547021</v>
+        <v>-147.0529702832426</v>
       </c>
       <c r="O81">
-        <v>-14.46649331547021</v>
+        <v>-14.70529702832427</v>
       </c>
       <c r="P81">
-        <v>-130.1984398392319</v>
+        <v>-132.3476732549184</v>
       </c>
       <c r="Q81">
-        <v>-101.3984398392319</v>
+        <v>-103.5476732549184</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2698078709730018</v>
+        <v>0.2810082645216518</v>
       </c>
       <c r="T81">
-        <v>4.48993759800663</v>
+        <v>4.714434477906962</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02331770458603753</v>
+        <v>0.02302623327871205</v>
       </c>
       <c r="W81">
-        <v>0.2303016852586124</v>
+        <v>0.2303704141928797</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2331770458603751</v>
+        <v>0.2302623327871206</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2404979842586341</v>
+        <v>0.2423979842586341</v>
       </c>
       <c r="C82">
-        <v>-542.4051259268165</v>
+        <v>-554.8885493485851</v>
       </c>
       <c r="D82">
-        <v>243.7855877425756</v>
+        <v>241.4295482416743</v>
       </c>
       <c r="E82">
-        <v>619.0523215826521</v>
+        <v>629.1797055035195</v>
       </c>
       <c r="F82">
-        <v>810.190713669392</v>
+        <v>820.3180975902594</v>
       </c>
       <c r="G82">
         <v>24</v>
@@ -8011,37 +8011,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M82">
-        <v>191.0429702832427</v>
+        <v>193.4310074117832</v>
       </c>
       <c r="N82">
-        <v>-147.0529702832426</v>
+        <v>-149.4410074117832</v>
       </c>
       <c r="O82">
-        <v>-14.70529702832427</v>
+        <v>-14.94410074117832</v>
       </c>
       <c r="P82">
-        <v>-132.3476732549184</v>
+        <v>-134.4969066706049</v>
       </c>
       <c r="Q82">
-        <v>-103.5476732549184</v>
+        <v>-105.6969066706049</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2810082645216518</v>
+        <v>0.2933876468648967</v>
       </c>
       <c r="T82">
-        <v>4.714434477906962</v>
+        <v>4.962562608323117</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02302623327871205</v>
+        <v>0.02274195879378968</v>
       </c>
       <c r="W82">
-        <v>0.2303704141928797</v>
+        <v>0.2304374461164244</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2302623327871206</v>
+        <v>0.2274195879378968</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2423979842586341</v>
+        <v>0.2442979842586341</v>
       </c>
       <c r="C83">
-        <v>-554.8885493485851</v>
+        <v>-567.3268692891427</v>
       </c>
       <c r="D83">
-        <v>241.4295482416743</v>
+        <v>239.1186122219841</v>
       </c>
       <c r="E83">
-        <v>629.1797055035195</v>
+        <v>639.3070894243868</v>
       </c>
       <c r="F83">
-        <v>820.3180975902594</v>
+        <v>830.4454815111268</v>
       </c>
       <c r="G83">
         <v>24</v>
@@ -8093,37 +8093,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M83">
-        <v>193.4310074117832</v>
+        <v>195.8190445403237</v>
       </c>
       <c r="N83">
-        <v>-149.4410074117832</v>
+        <v>-151.8290445403237</v>
       </c>
       <c r="O83">
-        <v>-14.94410074117832</v>
+        <v>-15.18290445403237</v>
       </c>
       <c r="P83">
-        <v>-134.4969066706049</v>
+        <v>-136.6461400862913</v>
       </c>
       <c r="Q83">
-        <v>-105.6969066706049</v>
+        <v>-107.8461400862913</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2933876468648967</v>
+        <v>0.3071425161351687</v>
       </c>
       <c r="T83">
-        <v>4.962562608323117</v>
+        <v>5.238260531007735</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02274195879378968</v>
+        <v>0.02246461783288981</v>
       </c>
       <c r="W83">
-        <v>0.2304374461164244</v>
+        <v>0.2305028431150046</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2274195879378968</v>
+        <v>0.2246461783288981</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2442979842586341</v>
+        <v>0.2461979842586342</v>
       </c>
       <c r="C84">
-        <v>-567.3268692891427</v>
+        <v>-579.7213686448412</v>
       </c>
       <c r="D84">
-        <v>239.1186122219841</v>
+        <v>236.8514967871531</v>
       </c>
       <c r="E84">
-        <v>639.3070894243868</v>
+        <v>649.4344733452543</v>
       </c>
       <c r="F84">
-        <v>830.4454815111268</v>
+        <v>840.5728654319943</v>
       </c>
       <c r="G84">
         <v>24</v>
@@ -8175,37 +8175,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M84">
-        <v>195.8190445403237</v>
+        <v>198.2070816688642</v>
       </c>
       <c r="N84">
-        <v>-151.8290445403237</v>
+        <v>-154.2170816688642</v>
       </c>
       <c r="O84">
-        <v>-15.18290445403237</v>
+        <v>-15.42170816688643</v>
       </c>
       <c r="P84">
-        <v>-136.6461400862913</v>
+        <v>-138.7953735019778</v>
       </c>
       <c r="Q84">
-        <v>-107.8461400862913</v>
+        <v>-109.9953735019778</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3071425161351687</v>
+        <v>0.3225156053195904</v>
       </c>
       <c r="T84">
-        <v>5.238260531007735</v>
+        <v>5.546393503419955</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02246461783288981</v>
+        <v>0.02219395978671041</v>
       </c>
       <c r="W84">
-        <v>0.2305028431150046</v>
+        <v>0.2305666642822937</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2246461783288981</v>
+        <v>0.2219395978671042</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2461979842586342</v>
+        <v>0.2480979842586342</v>
       </c>
       <c r="C85">
-        <v>-579.7213686448412</v>
+        <v>-592.0732821157424</v>
       </c>
       <c r="D85">
-        <v>236.8514967871531</v>
+        <v>234.6269672371193</v>
       </c>
       <c r="E85">
-        <v>649.4344733452543</v>
+        <v>659.5618572661217</v>
       </c>
       <c r="F85">
-        <v>840.5728654319943</v>
+        <v>850.7002493528616</v>
       </c>
       <c r="G85">
         <v>24</v>
@@ -8257,37 +8257,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M85">
-        <v>198.2070816688642</v>
+        <v>200.5951187974048</v>
       </c>
       <c r="N85">
-        <v>-154.2170816688642</v>
+        <v>-156.6051187974048</v>
       </c>
       <c r="O85">
-        <v>-15.42170816688643</v>
+        <v>-15.66051187974048</v>
       </c>
       <c r="P85">
-        <v>-138.7953735019778</v>
+        <v>-140.9446069176643</v>
       </c>
       <c r="Q85">
-        <v>-109.9953735019778</v>
+        <v>-112.1446069176643</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3225156053195904</v>
+        <v>0.339810330652065</v>
       </c>
       <c r="T85">
-        <v>5.546393503419955</v>
+        <v>5.893043097383704</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02219395978671041</v>
+        <v>0.02192974597972577</v>
       </c>
       <c r="W85">
-        <v>0.2305666642822937</v>
+        <v>0.2306289658979807</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2219395978671042</v>
+        <v>0.2192974597972577</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2480979842586341</v>
+        <v>0.2499979842586341</v>
       </c>
       <c r="C86">
-        <v>-592.0732821157421</v>
+        <v>-604.3837984478771</v>
       </c>
       <c r="D86">
-        <v>234.6269672371193</v>
+        <v>232.4438348258518</v>
       </c>
       <c r="E86">
-        <v>659.5618572661216</v>
+        <v>669.689241186989</v>
       </c>
       <c r="F86">
-        <v>850.7002493528615</v>
+        <v>860.8276332737289</v>
       </c>
       <c r="G86">
         <v>24</v>
@@ -8339,37 +8339,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M86">
-        <v>200.5951187974048</v>
+        <v>202.9831559259453</v>
       </c>
       <c r="N86">
-        <v>-156.6051187974048</v>
+        <v>-158.9931559259453</v>
       </c>
       <c r="O86">
-        <v>-15.66051187974048</v>
+        <v>-15.89931559259453</v>
       </c>
       <c r="P86">
-        <v>-140.9446069176643</v>
+        <v>-143.0938403333508</v>
       </c>
       <c r="Q86">
-        <v>-112.1446069176643</v>
+        <v>-114.2938403333508</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3398103306520647</v>
+        <v>0.3594110193622024</v>
       </c>
       <c r="T86">
-        <v>5.8930430973837</v>
+        <v>6.28591263720928</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02192974597972577</v>
+        <v>0.02167174896819958</v>
       </c>
       <c r="W86">
-        <v>0.2306289658979807</v>
+        <v>0.2306898015932985</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2192974597972576</v>
+        <v>0.2167174896819958</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2499979842586341</v>
+        <v>0.2518979842586341</v>
       </c>
       <c r="C87">
-        <v>-604.3837984478771</v>
+        <v>-616.6540625514779</v>
       </c>
       <c r="D87">
-        <v>232.4438348258518</v>
+        <v>230.3009546431185</v>
       </c>
       <c r="E87">
-        <v>669.689241186989</v>
+        <v>679.8166251078565</v>
       </c>
       <c r="F87">
-        <v>860.8276332737289</v>
+        <v>870.9550171945964</v>
       </c>
       <c r="G87">
         <v>24</v>
@@ -8421,37 +8421,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M87">
-        <v>202.9831559259453</v>
+        <v>205.3711930544858</v>
       </c>
       <c r="N87">
-        <v>-158.9931559259453</v>
+        <v>-161.3811930544858</v>
       </c>
       <c r="O87">
-        <v>-15.89931559259453</v>
+        <v>-16.13811930544858</v>
       </c>
       <c r="P87">
-        <v>-143.0938403333508</v>
+        <v>-145.2430737490373</v>
       </c>
       <c r="Q87">
-        <v>-114.2938403333508</v>
+        <v>-116.4430737490373</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3594110193622024</v>
+        <v>0.3818118064595025</v>
       </c>
       <c r="T87">
-        <v>6.28591263720928</v>
+        <v>6.734906397009943</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02167174896819958</v>
+        <v>0.021419751887174</v>
       </c>
       <c r="W87">
-        <v>0.2306898015932985</v>
+        <v>0.2307492225050044</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2167174896819958</v>
+        <v>0.2141975188717401</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2518979842586341</v>
+        <v>0.2537979842586341</v>
       </c>
       <c r="C88">
-        <v>-616.6540625514779</v>
+        <v>-628.8851775031126</v>
       </c>
       <c r="D88">
-        <v>230.3009546431185</v>
+        <v>228.1972236123512</v>
       </c>
       <c r="E88">
-        <v>679.8166251078565</v>
+        <v>689.9440090287238</v>
       </c>
       <c r="F88">
-        <v>870.9550171945964</v>
+        <v>881.0824011154638</v>
       </c>
       <c r="G88">
         <v>24</v>
@@ -8503,37 +8503,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M88">
-        <v>205.3711930544858</v>
+        <v>207.7592301830264</v>
       </c>
       <c r="N88">
-        <v>-161.3811930544858</v>
+        <v>-163.7692301830264</v>
       </c>
       <c r="O88">
-        <v>-16.13811930544858</v>
+        <v>-16.37692301830264</v>
       </c>
       <c r="P88">
-        <v>-145.2430737490373</v>
+        <v>-147.3923071647237</v>
       </c>
       <c r="Q88">
-        <v>-116.4430737490373</v>
+        <v>-118.5923071647237</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3818118064595025</v>
+        <v>0.4076588684948489</v>
       </c>
       <c r="T88">
-        <v>6.734906397009943</v>
+        <v>7.252976119856863</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.021419751887174</v>
+        <v>0.02117354784249384</v>
       </c>
       <c r="W88">
-        <v>0.2307492225050044</v>
+        <v>0.23080727741874</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2141975188717401</v>
+        <v>0.2117354784249385</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2537979842586341</v>
+        <v>0.2556979842586342</v>
       </c>
       <c r="C89">
-        <v>-628.8851775031126</v>
+        <v>-641.0782064390804</v>
       </c>
       <c r="D89">
-        <v>228.1972236123512</v>
+        <v>226.1315785972508</v>
       </c>
       <c r="E89">
-        <v>689.9440090287238</v>
+        <v>700.0713929495912</v>
       </c>
       <c r="F89">
-        <v>881.0824011154638</v>
+        <v>891.2097850363311</v>
       </c>
       <c r="G89">
         <v>24</v>
@@ -8585,37 +8585,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M89">
-        <v>207.7592301830264</v>
+        <v>210.1472673115669</v>
       </c>
       <c r="N89">
-        <v>-163.7692301830264</v>
+        <v>-166.1572673115669</v>
       </c>
       <c r="O89">
-        <v>-16.37692301830264</v>
+        <v>-16.61572673115669</v>
       </c>
       <c r="P89">
-        <v>-147.3923071647237</v>
+        <v>-149.5415405804102</v>
       </c>
       <c r="Q89">
-        <v>-118.5923071647237</v>
+        <v>-120.7415405804102</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4076588684948489</v>
+        <v>0.437813774202753</v>
       </c>
       <c r="T89">
-        <v>7.252976119856863</v>
+        <v>7.857390796511601</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02117354784249384</v>
+        <v>0.02093293934428369</v>
       </c>
       <c r="W89">
-        <v>0.23080727741874</v>
+        <v>0.2308640129026179</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2117354784249385</v>
+        <v>0.2093293934428369</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2556979842586342</v>
+        <v>0.2575979842586341</v>
       </c>
       <c r="C90">
-        <v>-641.0782064390804</v>
+        <v>-653.2341743468951</v>
       </c>
       <c r="D90">
-        <v>226.1315785972508</v>
+        <v>224.1029946103035</v>
       </c>
       <c r="E90">
-        <v>700.0713929495912</v>
+        <v>710.1987768704587</v>
       </c>
       <c r="F90">
-        <v>891.2097850363311</v>
+        <v>901.3371689571986</v>
       </c>
       <c r="G90">
         <v>24</v>
@@ -8667,37 +8667,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M90">
-        <v>210.1472673115669</v>
+        <v>212.5353044401074</v>
       </c>
       <c r="N90">
-        <v>-166.1572673115669</v>
+        <v>-168.5453044401074</v>
       </c>
       <c r="O90">
-        <v>-16.61572673115669</v>
+        <v>-16.85453044401075</v>
       </c>
       <c r="P90">
-        <v>-149.5415405804102</v>
+        <v>-151.6907739960967</v>
       </c>
       <c r="Q90">
-        <v>-120.7415405804102</v>
+        <v>-122.8907739960967</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.437813774202753</v>
+        <v>0.473451390039367</v>
       </c>
       <c r="T90">
-        <v>7.857390796511601</v>
+        <v>8.57169905073993</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02093293934428369</v>
+        <v>0.02069773777861758</v>
       </c>
       <c r="W90">
-        <v>0.2308640129026179</v>
+        <v>0.230919473431802</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2093293934428369</v>
+        <v>0.2069773777861759</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2575979842586341</v>
+        <v>0.2594979842586341</v>
       </c>
       <c r="C91">
-        <v>-653.2341743468951</v>
+        <v>-665.3540697611991</v>
       </c>
       <c r="D91">
-        <v>224.1029946103035</v>
+        <v>222.1104831168669</v>
       </c>
       <c r="E91">
-        <v>710.1987768704587</v>
+        <v>720.3261607913261</v>
       </c>
       <c r="F91">
-        <v>901.3371689571986</v>
+        <v>911.464552878066</v>
       </c>
       <c r="G91">
         <v>24</v>
@@ -8749,37 +8749,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M91">
-        <v>212.5353044401074</v>
+        <v>214.923341568648</v>
       </c>
       <c r="N91">
-        <v>-168.5453044401074</v>
+        <v>-170.933341568648</v>
       </c>
       <c r="O91">
-        <v>-16.85453044401075</v>
+        <v>-17.0933341568648</v>
       </c>
       <c r="P91">
-        <v>-151.6907739960967</v>
+        <v>-153.8400074117832</v>
       </c>
       <c r="Q91">
-        <v>-122.8907739960967</v>
+        <v>-125.0400074117832</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.473451390039367</v>
+        <v>0.5162165290433036</v>
       </c>
       <c r="T91">
-        <v>8.57169905073993</v>
+        <v>9.428868955813922</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02069773777861758</v>
+        <v>0.02046776291441071</v>
       </c>
       <c r="W91">
-        <v>0.230919473431802</v>
+        <v>0.2309737015047819</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2069773777861759</v>
+        <v>0.2046776291441073</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2594979842586341</v>
+        <v>0.2613979842586341</v>
       </c>
       <c r="C92">
-        <v>-665.3540697611991</v>
+        <v>-677.4388463700046</v>
       </c>
       <c r="D92">
-        <v>222.1104831168669</v>
+        <v>220.1530904289288</v>
       </c>
       <c r="E92">
-        <v>720.3261607913261</v>
+        <v>730.4535447121934</v>
       </c>
       <c r="F92">
-        <v>911.464552878066</v>
+        <v>921.5919367989334</v>
       </c>
       <c r="G92">
         <v>24</v>
@@ -8831,37 +8831,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M92">
-        <v>214.923341568648</v>
+        <v>217.3113786971885</v>
       </c>
       <c r="N92">
-        <v>-170.933341568648</v>
+        <v>-173.3213786971885</v>
       </c>
       <c r="O92">
-        <v>-17.0933341568648</v>
+        <v>-17.33213786971885</v>
       </c>
       <c r="P92">
-        <v>-153.8400074117832</v>
+        <v>-155.9892408274696</v>
       </c>
       <c r="Q92">
-        <v>-125.0400074117832</v>
+        <v>-127.1892408274696</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5162165290433036</v>
+        <v>0.5684850322703374</v>
       </c>
       <c r="T92">
-        <v>9.428868955813922</v>
+        <v>10.47652106201547</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02046776291441071</v>
+        <v>0.02024284244282379</v>
       </c>
       <c r="W92">
-        <v>0.2309737015047819</v>
+        <v>0.2310267377519822</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2046776291441073</v>
+        <v>0.2024284244282379</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2613979842586341</v>
+        <v>0.2632979842586341</v>
       </c>
       <c r="C93">
-        <v>-677.4388463700046</v>
+        <v>-689.4894245367441</v>
       </c>
       <c r="D93">
-        <v>220.1530904289288</v>
+        <v>218.2298961830568</v>
       </c>
       <c r="E93">
-        <v>730.4535447121934</v>
+        <v>740.5809286330609</v>
       </c>
       <c r="F93">
-        <v>921.5919367989334</v>
+        <v>931.7193207198009</v>
       </c>
       <c r="G93">
         <v>24</v>
@@ -8913,37 +8913,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M93">
-        <v>217.3113786971885</v>
+        <v>219.6994158257291</v>
       </c>
       <c r="N93">
-        <v>-173.3213786971885</v>
+        <v>-175.7094158257291</v>
       </c>
       <c r="O93">
-        <v>-17.33213786971885</v>
+        <v>-17.57094158257291</v>
       </c>
       <c r="P93">
-        <v>-155.9892408274696</v>
+        <v>-158.1384742431562</v>
       </c>
       <c r="Q93">
-        <v>-127.1892408274696</v>
+        <v>-129.3384742431562</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5684850322703374</v>
+        <v>0.6338206613041298</v>
       </c>
       <c r="T93">
-        <v>10.47652106201547</v>
+        <v>11.78608619476741</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02024284244282379</v>
+        <v>0.02002281154670613</v>
       </c>
       <c r="W93">
-        <v>0.2310267377519822</v>
+        <v>0.2310786210372867</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2024284244282379</v>
+        <v>0.2002281154670612</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2632979842586341</v>
+        <v>0.2651979842586341</v>
       </c>
       <c r="C94">
-        <v>-689.4894245367441</v>
+        <v>-701.5066927432347</v>
       </c>
       <c r="D94">
-        <v>218.2298961830568</v>
+        <v>216.3400118974336</v>
       </c>
       <c r="E94">
-        <v>740.5809286330609</v>
+        <v>750.7083125539283</v>
       </c>
       <c r="F94">
-        <v>931.7193207198009</v>
+        <v>941.8467046406682</v>
       </c>
       <c r="G94">
         <v>24</v>
@@ -8995,37 +8995,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M94">
-        <v>219.6994158257291</v>
+        <v>222.0874529542696</v>
       </c>
       <c r="N94">
-        <v>-175.7094158257291</v>
+        <v>-178.0974529542696</v>
       </c>
       <c r="O94">
-        <v>-17.57094158257291</v>
+        <v>-17.80974529542696</v>
       </c>
       <c r="P94">
-        <v>-158.1384742431562</v>
+        <v>-160.2877076588426</v>
       </c>
       <c r="Q94">
-        <v>-129.3384742431562</v>
+        <v>-131.4877076588426</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6338206613041298</v>
+        <v>0.7178236129190055</v>
       </c>
       <c r="T94">
-        <v>11.78608619476741</v>
+        <v>13.4698127940199</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02002281154670613</v>
+        <v>0.01980751249781682</v>
       </c>
       <c r="W94">
-        <v>0.2310786210372867</v>
+        <v>0.2311293885530148</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2002281154670612</v>
+        <v>0.1980751249781683</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2651979842586341</v>
+        <v>0.2670979842586341</v>
       </c>
       <c r="C95">
-        <v>-701.5066927432347</v>
+        <v>-713.4915089583101</v>
       </c>
       <c r="D95">
-        <v>216.3400118974336</v>
+        <v>214.4825796032255</v>
       </c>
       <c r="E95">
-        <v>750.7083125539283</v>
+        <v>760.8356964747957</v>
       </c>
       <c r="F95">
-        <v>941.8467046406682</v>
+        <v>951.9740885615356</v>
       </c>
       <c r="G95">
         <v>24</v>
@@ -9077,37 +9077,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M95">
-        <v>222.0874529542696</v>
+        <v>224.4754900828101</v>
       </c>
       <c r="N95">
-        <v>-178.0974529542696</v>
+        <v>-180.4854900828101</v>
       </c>
       <c r="O95">
-        <v>-17.80974529542696</v>
+        <v>-18.04854900828101</v>
       </c>
       <c r="P95">
-        <v>-160.2877076588426</v>
+        <v>-162.4369410745291</v>
       </c>
       <c r="Q95">
-        <v>-131.4877076588426</v>
+        <v>-133.6369410745291</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7178236129190055</v>
+        <v>0.8298275484055068</v>
       </c>
       <c r="T95">
-        <v>13.4698127940199</v>
+        <v>15.71478159302322</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01980751249781682</v>
+        <v>0.01959679427975494</v>
       </c>
       <c r="W95">
-        <v>0.2311293885530148</v>
+        <v>0.2311790759088338</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1980751249781683</v>
+        <v>0.1959679427975495</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2670979842586341</v>
+        <v>0.2689979842586341</v>
       </c>
       <c r="C96">
-        <v>-713.4915089583101</v>
+        <v>-725.4447019365474</v>
       </c>
       <c r="D96">
-        <v>214.4825796032255</v>
+        <v>212.6567705458556</v>
       </c>
       <c r="E96">
-        <v>760.8356964747957</v>
+        <v>770.963080395663</v>
       </c>
       <c r="F96">
-        <v>951.9740885615356</v>
+        <v>962.101472482403</v>
       </c>
       <c r="G96">
         <v>24</v>
@@ -9159,37 +9159,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M96">
-        <v>224.4754900828101</v>
+        <v>226.8635272113506</v>
       </c>
       <c r="N96">
-        <v>-180.4854900828101</v>
+        <v>-182.8735272113506</v>
       </c>
       <c r="O96">
-        <v>-18.04854900828101</v>
+        <v>-18.28735272113506</v>
       </c>
       <c r="P96">
-        <v>-162.4369410745291</v>
+        <v>-164.5861744902156</v>
       </c>
       <c r="Q96">
-        <v>-133.6369410745291</v>
+        <v>-135.7861744902156</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8298275484055068</v>
+        <v>0.9866330580866085</v>
       </c>
       <c r="T96">
-        <v>15.71478159302322</v>
+        <v>18.85773791162787</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01959679427975494</v>
+        <v>0.01939051223470489</v>
       </c>
       <c r="W96">
-        <v>0.2311790759088338</v>
+        <v>0.2312277172150566</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1959679427975495</v>
+        <v>0.1939051223470489</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2689979842586341</v>
+        <v>0.2708979842586342</v>
       </c>
       <c r="C97">
-        <v>-725.4447019365474</v>
+        <v>-737.3670724512215</v>
       </c>
       <c r="D97">
-        <v>212.6567705458556</v>
+        <v>210.861783952049</v>
       </c>
       <c r="E97">
-        <v>770.963080395663</v>
+        <v>781.0904643165305</v>
       </c>
       <c r="F97">
-        <v>962.101472482403</v>
+        <v>972.2288564032705</v>
       </c>
       <c r="G97">
         <v>24</v>
@@ -9241,37 +9241,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M97">
-        <v>226.8635272113506</v>
+        <v>229.2515643398912</v>
       </c>
       <c r="N97">
-        <v>-182.8735272113506</v>
+        <v>-185.2615643398912</v>
       </c>
       <c r="O97">
-        <v>-18.28735272113506</v>
+        <v>-18.52615643398912</v>
       </c>
       <c r="P97">
-        <v>-164.5861744902156</v>
+        <v>-166.7354079059021</v>
       </c>
       <c r="Q97">
-        <v>-135.7861744902156</v>
+        <v>-137.9354079059021</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9866330580866085</v>
+        <v>1.221841322608261</v>
       </c>
       <c r="T97">
-        <v>18.85773791162787</v>
+        <v>23.57217238953485</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01939051223470489</v>
+        <v>0.01918852773226004</v>
       </c>
       <c r="W97">
-        <v>0.2312277172150566</v>
+        <v>0.2312753451607331</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1939051223470489</v>
+        <v>0.1918852773226004</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2708979842586341</v>
+        <v>0.2727979842586341</v>
       </c>
       <c r="C98">
-        <v>-737.3670724512212</v>
+        <v>-749.2593944653381</v>
       </c>
       <c r="D98">
-        <v>210.8617839520491</v>
+        <v>209.0968458587996</v>
       </c>
       <c r="E98">
-        <v>781.0904643165304</v>
+        <v>791.2178482373978</v>
       </c>
       <c r="F98">
-        <v>972.2288564032704</v>
+        <v>982.3562403241377</v>
       </c>
       <c r="G98">
         <v>24</v>
@@ -9323,37 +9323,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M98">
-        <v>229.2515643398912</v>
+        <v>231.6396014684317</v>
       </c>
       <c r="N98">
-        <v>-185.2615643398912</v>
+        <v>-187.6496014684317</v>
       </c>
       <c r="O98">
-        <v>-18.52615643398912</v>
+        <v>-18.76496014684317</v>
       </c>
       <c r="P98">
-        <v>-166.735407905902</v>
+        <v>-168.8846413215885</v>
       </c>
       <c r="Q98">
-        <v>-137.935407905902</v>
+        <v>-140.0846413215885</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.221841322608258</v>
+        <v>1.613855096811011</v>
       </c>
       <c r="T98">
-        <v>23.57217238953478</v>
+        <v>31.42956318604638</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01918852773226004</v>
+        <v>0.01899070785873159</v>
       </c>
       <c r="W98">
-        <v>0.2312753451607331</v>
+        <v>0.2313219910869111</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1918852773226005</v>
+        <v>0.1899070785873159</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2727979842586341</v>
+        <v>0.2746979842586341</v>
       </c>
       <c r="C99">
-        <v>-749.2593944653381</v>
+        <v>-761.1224162443477</v>
       </c>
       <c r="D99">
-        <v>209.0968458587996</v>
+        <v>207.3612080006574</v>
       </c>
       <c r="E99">
-        <v>791.2178482373978</v>
+        <v>801.3452321582652</v>
       </c>
       <c r="F99">
-        <v>982.3562403241377</v>
+        <v>992.4836242450051</v>
       </c>
       <c r="G99">
         <v>24</v>
@@ -9405,37 +9405,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M99">
-        <v>231.6396014684317</v>
+        <v>234.0276385969722</v>
       </c>
       <c r="N99">
-        <v>-187.6496014684317</v>
+        <v>-190.0376385969722</v>
       </c>
       <c r="O99">
-        <v>-18.76496014684317</v>
+        <v>-19.00376385969722</v>
       </c>
       <c r="P99">
-        <v>-168.8846413215885</v>
+        <v>-171.033874737275</v>
       </c>
       <c r="Q99">
-        <v>-140.0846413215885</v>
+        <v>-142.233874737275</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.613855096811011</v>
+        <v>2.397882645216516</v>
       </c>
       <c r="T99">
-        <v>31.42956318604638</v>
+        <v>47.14434477906956</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01899070785873159</v>
+        <v>0.01879692512547923</v>
       </c>
       <c r="W99">
-        <v>0.2313219910869111</v>
+        <v>0.231367685055412</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1899070785873159</v>
+        <v>0.1879692512547924</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2746979842586341</v>
+        <v>0.2765979842586341</v>
       </c>
       <c r="C100">
-        <v>-761.1224162443477</v>
+        <v>-772.9568614138947</v>
       </c>
       <c r="D100">
-        <v>207.3612080006574</v>
+        <v>205.6541467519779</v>
       </c>
       <c r="E100">
-        <v>801.3452321582652</v>
+        <v>811.4726160791326</v>
       </c>
       <c r="F100">
-        <v>992.4836242450051</v>
+        <v>1002.611008165873</v>
       </c>
       <c r="G100">
         <v>24</v>
@@ -9487,37 +9487,37 @@
         <v>43.98999999999999</v>
       </c>
       <c r="M100">
-        <v>234.0276385969722</v>
+        <v>236.4156757255128</v>
       </c>
       <c r="N100">
-        <v>-190.0376385969722</v>
+        <v>-192.4256757255127</v>
       </c>
       <c r="O100">
-        <v>-19.00376385969722</v>
+        <v>-19.24256757255128</v>
       </c>
       <c r="P100">
-        <v>-171.033874737275</v>
+        <v>-173.1831081529615</v>
       </c>
       <c r="Q100">
-        <v>-142.233874737275</v>
+        <v>-144.3831081529615</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.397882645216516</v>
+        <v>4.749965290433032</v>
       </c>
       <c r="T100">
-        <v>47.14434477906956</v>
+        <v>94.28868955813913</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01879692512547923</v>
+        <v>0.01860705719491883</v>
       </c>
       <c r="W100">
-        <v>0.231367685055412</v>
+        <v>0.2314124559134381</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1879692512547924</v>
+        <v>0.1860705719491884</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2765979842586341</v>
-      </c>
-      <c r="C101">
-        <v>-772.9568614138947</v>
-      </c>
-      <c r="D101">
-        <v>205.6541467519779</v>
-      </c>
-      <c r="E101">
-        <v>811.4726160791326</v>
-      </c>
-      <c r="F101">
-        <v>1002.611008165873</v>
-      </c>
-      <c r="G101">
-        <v>24</v>
-      </c>
-      <c r="H101">
-        <v>821.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>72.78999999999999</v>
-      </c>
-      <c r="K101">
-        <v>28.8</v>
-      </c>
-      <c r="L101">
-        <v>43.98999999999999</v>
-      </c>
-      <c r="M101">
-        <v>236.4156757255128</v>
-      </c>
-      <c r="N101">
-        <v>-192.4256757255127</v>
-      </c>
-      <c r="O101">
-        <v>-19.24256757255128</v>
-      </c>
-      <c r="P101">
-        <v>-173.1831081529615</v>
-      </c>
-      <c r="Q101">
-        <v>-144.3831081529615</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.749965290433032</v>
-      </c>
-      <c r="T101">
-        <v>94.28868955813913</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01860705719491883</v>
-      </c>
-      <c r="W101">
-        <v>0.2314124559134381</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1860705719491884</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
